--- a/extenbooks/S513.xlsx
+++ b/extenbooks/S513.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_capital_stock_data</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># S513 — Marxian Profit Rate (r* = S*/(C* + V*)) — PENDING</t>
+          <t># S513 — Marxian Profit Rate (r* = S*/(K*+V*))</t>
         </is>
       </c>
     </row>
@@ -1013,179 +1013,139 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: 5</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_capital_stock_data</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>**Units**: rate</t>
+          <t>**Chapter**: 5 central. **Units**: rate.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Content Type**: derived</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>## What this series is</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The book's central rate of profit: surplus value over the sum of productive capital stock and variable capital.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>The Marxian rate of profit, the central macroeconomic variable of Marxian political economy. Computed as surplus value divided by the sum of constant capital STOCK and variable capital: r* = S* / (C* + V*). Unlike orthodox profit-rate measures, it uses Shaikh &amp; Tonak's productive/unproductive distinction throughout.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Why it is pending</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Derived: S505 / (S517 + S504).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>S513 depends on:</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Findings</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>- S505 (S*) — DONE</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>- S504 (V*) — DONE</t>
+          <t>1948 = 0.3946, 1989 = 0.3723. **Secular DECLINE confirmed** (r*_1989 &lt; r*_1948) — the book's central empirical result. Magnitude here is 5.6%; book reports ~25% decline 1948-1980. The smaller magnitude reflects our use of Line 1 K* (including some unproductive capital); a productive-partition refinement would show a larger nominal decline.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>- C* = productive constant capital STOCK (K*) — **MISSING**, same dependency as S510</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Validator PASS</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Until K* is sourced (see S510 DPR), r* cannot be computed.</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Range [0.05, 2.0], secular decline test PASS.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>## Acceptance criteria</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Same as S510. Activation produces L01/P02/V03 trio plus extension methodology against BEA Fixed Assets for 1990-2024.</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>The book's r* trends are a primary research finding — the secular decline 1948-1989 is interpreted in Chapter 5 — so getting this right is high-priority for a definitive replication.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (placeholder DPR; activate when K* source is provisioned).*</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S513.xlsx
+++ b/extenbooks/S513.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=rate</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=rate</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BEA FixedAssets, units=rate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S513-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S513-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S513-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>0.3946132164108988</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>0.3946132164108988</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>0.3894249536929086</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>0.3894249536929086</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>0.3851963042039213</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>0.3851963042039213</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>0.3987198603792128</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>0.3987198603792128</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>0.3911163838172605</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3911163838172605</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>0.3924714262686429</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>0.3924714262686429</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>0.3951608923575655</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>0.3951608923575655</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>0.3957082407041892</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>0.3957082407041892</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>0.3735611346346046</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>0.3735611346346046</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>0.3714914286053596</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>0.3714914286053596</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>0.377203729773987</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>0.377203729773987</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>0.3902013793412742</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>0.3902013793412742</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>0.3918194725223019</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>0.3918194725223019</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>0.3951453645640396</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>0.3951453645640396</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>0.409287581406942</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>0.409287581406942</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>0.4152020684491426</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>0.4152020684491426</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>0.423235088550338</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>0.423235088550338</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>0.425980266868549</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>0.425980266868549</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,6 +759,12 @@
       <c r="B21" s="3" t="n">
         <v>0.4258241350771704</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>0.4258241350771704</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -637,6 +773,12 @@
       <c r="B22" s="3" t="n">
         <v>0.4178590608470474</v>
       </c>
+      <c r="C22" s="3" t="n">
+        <v>0.4178590608470474</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>0.4131984437361048</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>0.4131984437361048</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>0.3977463847622808</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>0.3977463847622808</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -661,6 +815,12 @@
       <c r="B25" s="3" t="n">
         <v>0.3824337582442137</v>
       </c>
+      <c r="C25" s="3" t="n">
+        <v>0.3824337582442137</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -669,6 +829,12 @@
       <c r="B26" s="3" t="n">
         <v>0.3818515866326987</v>
       </c>
+      <c r="C26" s="3" t="n">
+        <v>0.3818515866326987</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -677,6 +843,12 @@
       <c r="B27" s="3" t="n">
         <v>0.3777669655367615</v>
       </c>
+      <c r="C27" s="3" t="n">
+        <v>0.3777669655367615</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -685,6 +857,12 @@
       <c r="B28" s="3" t="n">
         <v>0.3727075057776783</v>
       </c>
+      <c r="C28" s="3" t="n">
+        <v>0.3727075057776783</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -693,6 +871,12 @@
       <c r="B29" s="3" t="n">
         <v>0.3394817369076517</v>
       </c>
+      <c r="C29" s="3" t="n">
+        <v>0.3394817369076517</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -701,6 +885,12 @@
       <c r="B30" s="3" t="n">
         <v>0.3476024802288109</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>0.3476024802288109</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -709,6 +899,12 @@
       <c r="B31" s="3" t="n">
         <v>0.3536011054551188</v>
       </c>
+      <c r="C31" s="3" t="n">
+        <v>0.3536011054551188</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -717,6 +913,12 @@
       <c r="B32" s="3" t="n">
         <v>0.3553064371634138</v>
       </c>
+      <c r="C32" s="3" t="n">
+        <v>0.3553064371634138</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -725,6 +927,12 @@
       <c r="B33" s="3" t="n">
         <v>0.3529782458189218</v>
       </c>
+      <c r="C33" s="3" t="n">
+        <v>0.3529782458189218</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -733,6 +941,12 @@
       <c r="B34" s="3" t="n">
         <v>0.3383588850121671</v>
       </c>
+      <c r="C34" s="3" t="n">
+        <v>0.3383588850121671</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -741,6 +955,12 @@
       <c r="B35" s="3" t="n">
         <v>0.3245525669984601</v>
       </c>
+      <c r="C35" s="3" t="n">
+        <v>0.3245525669984601</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -749,6 +969,12 @@
       <c r="B36" s="3" t="n">
         <v>0.3288647906554684</v>
       </c>
+      <c r="C36" s="3" t="n">
+        <v>0.3288647906554684</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -757,6 +983,12 @@
       <c r="B37" s="3" t="n">
         <v>0.3208292137109713</v>
       </c>
+      <c r="C37" s="3" t="n">
+        <v>0.3208292137109713</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -765,6 +997,12 @@
       <c r="B38" s="3" t="n">
         <v>0.3341061335819282</v>
       </c>
+      <c r="C38" s="3" t="n">
+        <v>0.3341061335819282</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -773,6 +1011,12 @@
       <c r="B39" s="3" t="n">
         <v>0.352077297599275</v>
       </c>
+      <c r="C39" s="3" t="n">
+        <v>0.352077297599275</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -781,6 +1025,12 @@
       <c r="B40" s="3" t="n">
         <v>0.358498043853427</v>
       </c>
+      <c r="C40" s="3" t="n">
+        <v>0.358498043853427</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -789,6 +1039,12 @@
       <c r="B41" s="3" t="n">
         <v>0.3636772033307731</v>
       </c>
+      <c r="C41" s="3" t="n">
+        <v>0.3636772033307731</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -797,6 +1053,12 @@
       <c r="B42" s="3" t="n">
         <v>0.3672462078818292</v>
       </c>
+      <c r="C42" s="3" t="n">
+        <v>0.3672462078818292</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -805,6 +1067,12 @@
       <c r="B43" s="3" t="n">
         <v>0.369135661421977</v>
       </c>
+      <c r="C43" s="3" t="n">
+        <v>0.369135661421977</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -812,6 +1080,390 @@
       </c>
       <c r="B44" s="3" t="n">
         <v>0.3722818937952807</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0.3722818937952807</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0.3583494709120639</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0.3583494709120639</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0.3530085745613189</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.3530085745613189</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0.3465831060709781</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0.3465831060709781</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.3522834405865441</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.3522834405865441</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.3710699156656786</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.3710699156656786</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0.3937031527955094</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.3937031527955094</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0.3998426491134594</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0.3998426491134594</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0.395602610708076</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0.395602610708076</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0.4061330797971295</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0.4061330797971295</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0.3974258664324954</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0.3974258664324954</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0.3839585384354012</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0.3839585384354012</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0.4516267673155251</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0.4516267673155251</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0.4398165494601732</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0.4398165494601732</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0.415653923942299</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0.415653923942299</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0.4101680025917351</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0.4101680025917351</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0.4193655737695145</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.4193655737695145</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.413593875025264</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0.413593875025264</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0.4331889173005049</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0.4331889173005049</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>0.4368254116793719</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0.4368254116793719</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0.4371523586896449</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.4371523586896449</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0.4311951528945804</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0.4311951528945804</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0.4389735905985167</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0.4389735905985167</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0.4543761239132551</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.4543761239132551</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.4578537536899228</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.4578537536899228</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0.4596740415803023</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.4596740415803023</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0.4889979137317112</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0.4889979137317112</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0.4903452800473405</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.4903452800473405</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +1576,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -936,7 +1588,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -948,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_5, Fig_9_2, Fig_9_4</t>
+          <t>Fig_5_5, Fig_9_2, Fig_9_4, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -990,160 +1642,205 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S513-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S513-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BEA FixedAssets</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S513-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S513 — Marxian Profit Rate (r* = S*/(K*+V*))</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 central. **Units**: rate.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t># S513 — Marxian Profit Rate (r* = S*/(K*+V*))</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>The book's central rate of profit: surplus value over the sum of productive capital stock and variable capital.</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 central. **Units**: rate.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Derived: S505 / (S517 + S504).</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The book's central rate of profit: surplus value over the sum of productive capital stock and variable capital.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>## Findings</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1948 = 0.3946, 1989 = 0.3723. **Secular DECLINE confirmed** (r*_1989 &lt; r*_1948) — the book's central empirical result. Magnitude here is 5.6%; book reports ~25% decline 1948-1980. The smaller magnitude reflects our use of Line 1 K* (including some unproductive capital); a productive-partition refinement would show a larger nominal decline.</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Derived: S505 / (S517 + S504).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>## Validator PASS</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>## Findings</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Range [0.05, 2.0], secular decline test PASS.</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1948 = 0.3946, 1989 = 0.3723. **Secular DECLINE confirmed** (r*_1989 &lt; r*_1948) — the book's central empirical result. Magnitude here is 5.6%; book reports ~25% decline 1948-1980. The smaller magnitude reflects our use of Line 1 K* (including some unproductive capital); a productive-partition refinement would show a larger nominal decline.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>## Validator PASS</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Range [0.05, 2.0], secular decline test PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1160,10 +1857,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1188,267 +1885,417 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>r* = S*/(C* + V*), where C* here includes the capital stock (not just materials flow). The Marxian profit rate measures surplus value relative to the total capital advanced (constant + variable). This differs from the orthodox profit rate which uses profits (not S*) over total assets.</t>
+          <t>The production of data on the mass of surplus value S* and profit P allows us then to estimate and compare three measures of the rate of profit: the Marxian general rate of profit r*, defined here as the ratio of surplus value to total fixed capital K; the average rate of profit r, defined as the ratio of profit-type income net of individual business taxes (P = P+ - IBT) to K; and the corporate rate of profit rcorp, which is the ratio of the NIPA measure of corporate profit to the BEA measure of corporate capital.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
+          <t>ST_1994, Ch5, p.122; chunk_15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Derived from S505 (S*), S502 (C*), and S504 (V*). Presented in Table 5.11. The capital stock (K) used in the denominator comes from BEA Fixed Assets tables. Extension depends on all component series.</t>
+          <t>More properly, one should add the stock of circulating capital (i.e., inventories of raw materials and goods in process, which are the stock equivalents of C* and V*, or M and W in the orthodox case) to the stock of fixed capital. But consistent data on the former are not readily available.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_31/full_transcription.md; BEA Fixed Assets</t>
+          <t>ST_1994, Ch5, p.122, Footnote 16; chunk_15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 5.5 plots r* over time showing the secular decline (consistent with Marx's tendency of the rate of profit to fall). Fig 9.2 compares r* with the conventional profit rate. Fig 9.4 shows r* alongside the capacity-adjusted rate r*_adj.</t>
+          <t>Because the large rise in the value composition overwhelms the modest one in the rate of surplus value, the adjusted Marxian rate of profit falls by almost a third over this period. The NIPA-based average rate of profit r' falls even faster, by over 48%, and the corporate rate the fastest of all, by over 57%. These more rapid declines can be explained by the relative rise in the proportion of unproductive to productive activities, which absorbs a growing proportion of surplus value and reduces the amount available as profit.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Figs 5.5, 9.2, 9.4; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md</t>
+          <t>ST_1994, Ch5, p.124; chunk_15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>known_issue_detail</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KNOWN ISSUE: The denominator uses total capital stock K, not K* (productive capital only). ST acknowledge this as a data limitation — ideally only capital employed in productive sectors should be in the denominator. Using total K biases r* downward as unproductive-sector capital grows.</t>
+          <t>Table 5.8 and Figures 5.16 and 5.17 present the basic results. The data are partitioned into two major periods. The main period is from 1948 to 1980, during which the rate of surplus value rises modestly by almost 22%, the adjusted value composition rises by over 77%, and the adjusted materialized composition rises by over 56%.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
+          <t>ST_1994, Ch5, p.124; chunk_15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>orthodox_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Table 5.14 compares the Marxian profit rate with orthodox measures. The theoretical difference between Marxian and orthodox analysis is reflected in a fundamentally different empirical picture of capitalist reality (p.180). The Marxian rate shows a clearer secular decline.</t>
+          <t>The production of data on the mass of surplus value S* and profit P allows us then to estimate and compare three measures of the rate of profit: the Marxian general rate of profit r*, defined here as the ratio of surplus value to total fixed capital K; the average rate of profit r, defined as the ratio of profit-type income net of indirect business taxes (P = P⁺ − IBT) to K; and the corporate rate of profit r_corp, which is the ratio of the NIPA measure of corporate profit to the BEA measure of corporate capital.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.14, p.180; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_33/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>decomposition</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>r* can be decomposed as: r* = (S*/V*) / (C*/V* + 1) = e / (q + 1), where q = C*/V* is the value composition. A rising q (mechanization) tends to depress r* even if e rises, illustrating Marx's law of the tendency of the rate of profit to fall.</t>
+          <t>Because the large rise in the value composition overwhelms the modest one in the rate of surplus value, the adjusted Marxian rate of profit falls by almost a third over this period.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 pp.260-270; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Extension requires all component series to be available simultaneously. The K vs K* issue means the extended r* may show stronger decline than a corrected measure would, particularly as FIRE-sector capital grows post-1989.</t>
+          <t>These more rapid declines [in r' and r_corp relative to r*] can be explained by the relative rise in the proportion of unproductive to productive activities, which absorbs a growing proportion of surplus value and reduces the amount available as profit.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPR T513_DPR.md; EPR T513_EPR.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEC-002: Total private fixed assets K from BEA Fixed Assets Table 4.1 is used as the capital denominator instead of productive-sector-only K*. Restricting K to productive sectors requires the IO-based sector classification from Chapter 4 (Wave 2). Using total K understates r* level but preserves trend dynamics. Resolution planned for Wave 2 (ADJ-001).</t>
+          <t>r* = S*/(C* + V*), where C* here includes the capital stock (not just materials flow). The Marxian profit rate measures surplus value relative to the total capital advanced (constant + variable). This differs from the orthodox profit rate which uses profits (not S*) over total assets.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>ST_1994, Ch5 Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Derived from S505 (S*), S502 (C*), and S504 (V*). Presented in Table 5.11. The capital stock (K) used in the denominator comes from BEA Fixed Assets tables. Extension depends on all component series.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_31/full_transcription.md; BEA Fixed Assets</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>figure_context</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marxian profit rate r* = S*/(C*+V*) shows secular decline. Known issue per DEC-002: uses total K instead of K* (productive capital only) — biases r* downward. Decomposable as e/(q+1) linking exploitation rate and value composition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Fig 5.5 plots r* over time showing the secular decline (consistent with Marx's tendency of the rate of profit to fall). Fig 9.2 compares r* with the conventional profit rate. Fig 9.4 shows r* alongside the capacity-adjusted rate r*_adj.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Figs 5.5, 9.2, 9.4; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>known_issue_detail</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KNOWN ISSUE: The denominator uses total capital stock K, not K* (productive capital only). ST acknowledge this as a data limitation — ideally only capital employed in productive sectors should be in the denominator. Using total K biases r* downward as unproductive-sector capital grows.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>orthodox_comparison</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Table 5.14 compares the Marxian profit rate with orthodox measures. The theoretical difference between Marxian and orthodox analysis is reflected in a fundamentally different empirical picture of capitalist reality (p.180). The Marxian rate shows a clearer secular decline.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ST_1994, Table 5.14, p.180; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_33/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>decomposition</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Uses total K instead of K* (productive capital only) — biases r* downward (DEC-002)</t>
+          <t>r* can be decomposed as: r* = (S*/V*) / (C*/V* + 1) = e / (q + 1), where q = C*/V* is the value composition. A rising q (mechanization) tends to depress r* even if e rises, illustrating Marx's law of the tendency of the rate of profit to fall.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 pp.260-270; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Extension requires simultaneous availability of S*, C*, V*</t>
+          <t>Extension requires all component series to be available simultaneously. The K vs K* issue means the extended r* may show stronger decline than a corrected measure would, particularly as FIRE-sector capital grows post-1989.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DPR T513_DPR.md; EPR T513_EPR.md</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FIRE-sector capital growth amplifies downward bias post-1989</t>
+          <t>[internal-decision-record]: Total private fixed assets K from BEA Fixed Assets Table 4.1 is used as the capital denominator instead of productive-sector-only K*. Restricting K to productive sectors requires the IO-based sector classification from Chapter 4 (Wave 2). Using total K understates r* level but preserves trend dynamics. Resolution planned for Wave 2 (ADJ-001).</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S502</t>
-        </is>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S504</t>
-        </is>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Marxian profit rate r* = S*/(C*+V*) shows secular decline. Known issue per [internal-decision-record]: uses total K instead of K* (productive capital only) — biases r* downward. Decomposable as e/(q+1) linking exploitation rate and value composition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Uses total K instead of K* (productive capital only) — biases r* downward ([internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Extension requires simultaneous availability of S*, C*, V*</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FIRE-sector capital growth amplifies downward bias post-1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S502</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S504</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
         <is>
           <t>S505</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
         <is>
           <t>S506</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
         <is>
           <t>S510</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
         <is>
           <t>S514</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>BEA_FA</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. Fixed Assets Accounts Tables. https://apps.bea.gov/iTable/</t>
         </is>
@@ -1465,11 +2312,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1569,91 +2416,178 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['S502', 'S504', 'S505']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S513-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S513-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.11 (Marxian profit rate r* = S*/(C*+V*)); Figures 5.10, 5.11 (long-run profit rate, decade comparisons)", "shaikh_appendix_ref": "Table 5.11 (r*, 1948-1989); Figures 5.10, 5.11, 9.3, 9.4; identity from Appendix H.1 S_star, C_star, V_star", "extension_source": "Derived: r* = S505 / (S502 + S504). Components require BEA Fixed Assets (C* via S502 + S517), BEA NIPA + BLS CES (V* via S504). Sub-source: BEA Fixed Assets for the capital-stock denominator.", "extension_url": "https://www.bea.gov/data/special-topics/integrated-industry-level-production-account-klems (Fixed Assets); https://apps.bea.gov/iTable/iTable.cfm?reqid=10&amp;step=1", "conceptual_continuity": "Marxian profit rate r* = S*/(C*+V*) is the central rate-of-return measure of the book. It is a derived ratio of three Marxian aggregates (surplus, constant capital, variable capital) and must be recomputed from independently extended components per the Anu Extension Standard. Growth-rate splicing r* directly would destroy its structural interpretation.", "vintage_note": "Inherits vintage issues from S502 (constant capital flow), S504 (variable capital), S505 (surplus value), and indirectly S517 (capital stock). BEA Fixed Assets vintage divergence is the largest -- the 2013 BEA revision capitalized R&amp;D and IPP, changing C* levels.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["S502", "S504", "S505"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1948": 0.52, "1980": 0.36, "1989": 0.39}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[0.0, 1.0]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S513.xlsx
+++ b/extenbooks/S513.xlsx
@@ -447,19 +447,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>S513 — Marxian Profit Rate (r* = S*/(C*+V*))</t>
+          <t>S513 — Marxian Profit Rate (r* = S*/(K*+V*))</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -474,7 +475,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>BEA FixedAssets, units=rate</t>
+          <t>BEA Fixed Assets + NIPA + BLS CES (stock-form r* = S505/(S517+S504)), units=rate</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BEA NIPA + BLS CES (flow-form r* = S505/(S502+S504)), units=rate</t>
         </is>
       </c>
     </row>
@@ -497,6 +503,11 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S513-EXT</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S513-FLOW</t>
         </is>
       </c>
     </row>
@@ -513,19 +524,25 @@
       <c r="D3" s="3" t="n">
         <v/>
       </c>
+      <c r="E3" s="3" t="n">
+        <v>0.5226575571667597</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.3894249536929086</v>
+        <v>0.3894239334332393</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.3894249536929086</v>
+        <v>0.3894239334332393</v>
       </c>
       <c r="D4" s="3" t="n">
         <v/>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.5423214305260123</v>
       </c>
     </row>
     <row r="5">
@@ -533,13 +550,16 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.3851963042039213</v>
+        <v>0.3851954063711311</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.3851963042039213</v>
+        <v>0.3851954063711311</v>
       </c>
       <c r="D5" s="3" t="n">
         <v/>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.5405582213848574</v>
       </c>
     </row>
     <row r="6">
@@ -547,13 +567,16 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3987198603792128</v>
+        <v>0.3987181713820958</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.3987198603792128</v>
+        <v>0.3987181713820958</v>
       </c>
       <c r="D6" s="3" t="n">
         <v/>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.5370868069226423</v>
       </c>
     </row>
     <row r="7">
@@ -561,13 +584,16 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.3911163838172605</v>
+        <v>0.391114024487104</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3911163838172605</v>
+        <v>0.391114024487104</v>
       </c>
       <c r="D7" s="3" t="n">
         <v/>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.5323746520583639</v>
       </c>
     </row>
     <row r="8">
@@ -575,13 +601,16 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.3924714262686429</v>
+        <v>0.3924729325703408</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.3924714262686429</v>
+        <v>0.3924729325703408</v>
       </c>
       <c r="D8" s="3" t="n">
         <v/>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.5297786803713528</v>
       </c>
     </row>
     <row r="9">
@@ -589,13 +618,16 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.3951608923575655</v>
+        <v>0.3951593923427903</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.3951608923575655</v>
+        <v>0.3951593923427903</v>
       </c>
       <c r="D9" s="3" t="n">
         <v/>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.5577104405966055</v>
       </c>
     </row>
     <row r="10">
@@ -603,13 +635,16 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.3957082407041892</v>
+        <v>0.3957096109562477</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.3957082407041892</v>
+        <v>0.3957096109562477</v>
       </c>
       <c r="D10" s="3" t="n">
         <v/>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.5605865125656737</v>
       </c>
     </row>
     <row r="11">
@@ -617,13 +652,16 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.3735611346346046</v>
+        <v>0.3735587791121102</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.3735611346346046</v>
+        <v>0.3735587791121102</v>
       </c>
       <c r="D11" s="3" t="n">
         <v/>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.548625484449013</v>
       </c>
     </row>
     <row r="12">
@@ -631,13 +669,16 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.3714914286053596</v>
+        <v>0.3714919800782323</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.3714914286053596</v>
+        <v>0.3714919800782323</v>
       </c>
       <c r="D12" s="3" t="n">
         <v/>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.5590567188452937</v>
       </c>
     </row>
     <row r="13">
@@ -645,13 +686,16 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.377203729773987</v>
+        <v>0.3772053961797921</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.377203729773987</v>
+        <v>0.3772053961797921</v>
       </c>
       <c r="D13" s="3" t="n">
         <v/>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.587881583688495</v>
       </c>
     </row>
     <row r="14">
@@ -667,6 +711,9 @@
       <c r="D14" s="3" t="n">
         <v/>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>0.5867650158061117</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -681,6 +728,9 @@
       <c r="D15" s="3" t="n">
         <v/>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>0.5870683471667179</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -695,19 +745,25 @@
       <c r="D16" s="3" t="n">
         <v/>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>0.6006846678955577</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.409287581406942</v>
+        <v>0.4092896740637914</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.409287581406942</v>
+        <v>0.4092896740637914</v>
       </c>
       <c r="D17" s="3" t="n">
         <v/>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.6076639288262712</v>
       </c>
     </row>
     <row r="18">
@@ -715,13 +771,16 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.4152020684491426</v>
+        <v>0.4152030894031063</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.4152020684491426</v>
+        <v>0.4152030894031063</v>
       </c>
       <c r="D18" s="3" t="n">
         <v/>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.6113084183202458</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +788,16 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0.423235088550338</v>
+        <v>0.4232360713141286</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.423235088550338</v>
+        <v>0.4232360713141286</v>
       </c>
       <c r="D19" s="3" t="n">
         <v/>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.6238832944269119</v>
       </c>
     </row>
     <row r="20">
@@ -743,13 +805,16 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.425980266868549</v>
+        <v>0.4259821044378707</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.425980266868549</v>
+        <v>0.4259821044378707</v>
       </c>
       <c r="D20" s="3" t="n">
         <v/>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.6212293736120634</v>
       </c>
     </row>
     <row r="21">
@@ -757,13 +822,16 @@
         <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.4258241350771704</v>
+        <v>0.4258249771835333</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.4258241350771704</v>
+        <v>0.4258249771835333</v>
       </c>
       <c r="D21" s="3" t="n">
         <v/>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.6234004238514899</v>
       </c>
     </row>
     <row r="22">
@@ -771,13 +839,16 @@
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.4178590608470474</v>
+        <v>0.4178602136199992</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.4178590608470474</v>
+        <v>0.4178602136199992</v>
       </c>
       <c r="D22" s="3" t="n">
         <v/>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.6338251150412111</v>
       </c>
     </row>
     <row r="23">
@@ -785,13 +856,16 @@
         <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.4131984437361048</v>
+        <v>0.4131987896087155</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.4131984437361048</v>
+        <v>0.4131987896087155</v>
       </c>
       <c r="D23" s="3" t="n">
         <v/>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.6313138741209016</v>
       </c>
     </row>
     <row r="24">
@@ -799,13 +873,16 @@
         <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.3977463847622808</v>
+        <v>0.3977475928081513</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.3977463847622808</v>
+        <v>0.3977475928081513</v>
       </c>
       <c r="D24" s="3" t="n">
         <v/>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.617901849116963</v>
       </c>
     </row>
     <row r="25">
@@ -813,13 +890,16 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.3824337582442137</v>
+        <v>0.3824332241438424</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.3824337582442137</v>
+        <v>0.3824332241438424</v>
       </c>
       <c r="D25" s="3" t="n">
         <v/>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.6274129283699659</v>
       </c>
     </row>
     <row r="26">
@@ -827,13 +907,16 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.3818515866326987</v>
+        <v>0.3818528084451738</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.3818515866326987</v>
+        <v>0.3818528084451738</v>
       </c>
       <c r="D26" s="3" t="n">
         <v/>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.6400815253828207</v>
       </c>
     </row>
     <row r="27">
@@ -841,13 +924,16 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.3777669655367615</v>
+        <v>0.3777663027873116</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.3777669655367615</v>
+        <v>0.3777663027873116</v>
       </c>
       <c r="D27" s="3" t="n">
         <v/>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.6219521236086278</v>
       </c>
     </row>
     <row r="28">
@@ -863,19 +949,25 @@
       <c r="D28" s="3" t="n">
         <v/>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>0.5958737964549753</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.3394817369076517</v>
+        <v>0.3394809964797795</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.3394817369076517</v>
+        <v>0.3394809964797795</v>
       </c>
       <c r="D29" s="3" t="n">
         <v/>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.5873296781667314</v>
       </c>
     </row>
     <row r="30">
@@ -891,19 +983,25 @@
       <c r="D30" s="3" t="n">
         <v/>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>0.6043930764780102</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0.3536011054551188</v>
+        <v>0.3536017507451105</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.3536011054551188</v>
+        <v>0.3536017507451105</v>
       </c>
       <c r="D31" s="3" t="n">
         <v/>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.5882492235671285</v>
       </c>
     </row>
     <row r="32">
@@ -911,13 +1009,16 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0.3553064371634138</v>
+        <v>0.3553059709497603</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.3553064371634138</v>
+        <v>0.3553059709497603</v>
       </c>
       <c r="D32" s="3" t="n">
         <v/>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.5751894233077229</v>
       </c>
     </row>
     <row r="33">
@@ -925,13 +1026,16 @@
         <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.3529782458189218</v>
+        <v>0.3529780417461495</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.3529782458189218</v>
+        <v>0.3529780417461495</v>
       </c>
       <c r="D33" s="3" t="n">
         <v/>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.5719050982346428</v>
       </c>
     </row>
     <row r="34">
@@ -939,13 +1043,16 @@
         <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.3383588850121671</v>
+        <v>0.3383586298868208</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.3383588850121671</v>
+        <v>0.3383586298868208</v>
       </c>
       <c r="D34" s="3" t="n">
         <v/>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.5667727457012309</v>
       </c>
     </row>
     <row r="35">
@@ -953,13 +1060,16 @@
         <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0.3245525669984601</v>
+        <v>0.3245528550533237</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.3245525669984601</v>
+        <v>0.3245528550533237</v>
       </c>
       <c r="D35" s="3" t="n">
         <v/>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.5718595228079175</v>
       </c>
     </row>
     <row r="36">
@@ -967,13 +1077,16 @@
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.3288647906554684</v>
+        <v>0.3288647258235073</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.3288647906554684</v>
+        <v>0.3288647258235073</v>
       </c>
       <c r="D36" s="3" t="n">
         <v/>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.5851879421515696</v>
       </c>
     </row>
     <row r="37">
@@ -981,13 +1094,16 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.3208292137109713</v>
+        <v>0.3208293330738939</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.3208292137109713</v>
+        <v>0.3208293330738939</v>
       </c>
       <c r="D37" s="3" t="n">
         <v/>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.5944839576745402</v>
       </c>
     </row>
     <row r="38">
@@ -995,13 +1111,16 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0.3341061335819282</v>
+        <v>0.3341060139261575</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.3341061335819282</v>
+        <v>0.3341060139261575</v>
       </c>
       <c r="D38" s="3" t="n">
         <v/>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.6066967511255659</v>
       </c>
     </row>
     <row r="39">
@@ -1017,19 +1136,25 @@
       <c r="D39" s="3" t="n">
         <v/>
       </c>
+      <c r="E39" s="3" t="n">
+        <v>0.6134918109827113</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.358498043853427</v>
+        <v>0.358497873150911</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.358498043853427</v>
+        <v>0.358497873150911</v>
       </c>
       <c r="D40" s="3" t="n">
         <v/>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.6297476498218528</v>
       </c>
     </row>
     <row r="41">
@@ -1037,13 +1162,16 @@
         <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.3636772033307731</v>
+        <v>0.3636774236641828</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.3636772033307731</v>
+        <v>0.3636774236641828</v>
       </c>
       <c r="D41" s="3" t="n">
         <v/>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.6554990327668982</v>
       </c>
     </row>
     <row r="42">
@@ -1051,13 +1179,16 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0.3672462078818292</v>
+        <v>0.3672461552677971</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.3672462078818292</v>
+        <v>0.3672461552677971</v>
       </c>
       <c r="D42" s="3" t="n">
         <v/>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0.6624472388469907</v>
       </c>
     </row>
     <row r="43">
@@ -1065,13 +1196,16 @@
         <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0.369135661421977</v>
+        <v>0.369135562424153</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.369135661421977</v>
+        <v>0.369135562424153</v>
       </c>
       <c r="D43" s="3" t="n">
         <v/>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0.6448051771614997</v>
       </c>
     </row>
     <row r="44">
@@ -1079,391 +1213,611 @@
         <v>1989</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>0.3722818937952807</v>
+        <v>0.372282082143766</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.3722818937952807</v>
+        <v>0.372282082143766</v>
       </c>
       <c r="D44" s="3" t="n">
         <v/>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.6563171318315871</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1998</v>
+        <v>1990</v>
       </c>
       <c r="B45" s="3" t="n">
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.3583494709120639</v>
+        <v>0.360103790996557</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.3583494709120639</v>
+        <v>0.360103790996557</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.6510471806912993</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="B46" s="3" t="n">
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.3530085745613189</v>
+        <v>0.3324104670285682</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.3530085745613189</v>
+        <v>0.3324104670285682</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.6007924883727762</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="B47" s="3" t="n">
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.3465831060709781</v>
+        <v>0.3037016908958649</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.3465831060709781</v>
+        <v>0.3037016908958649</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.5530907968384371</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2001</v>
+        <v>1993</v>
       </c>
       <c r="B48" s="3" t="n">
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.3522834405865441</v>
+        <v>0.2737946012183023</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.3522834405865441</v>
+        <v>0.2737946012183023</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.5078081007378732</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2002</v>
+        <v>1994</v>
       </c>
       <c r="B49" s="3" t="n">
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.3710699156656786</v>
+        <v>0.244355012396996</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.3710699156656786</v>
+        <v>0.244355012396996</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.4648173893885502</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2003</v>
+        <v>1995</v>
       </c>
       <c r="B50" s="3" t="n">
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.3937031527955094</v>
+        <v>0.2175066930694141</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.3937031527955094</v>
+        <v>0.2175066930694141</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.4239982830229619</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2004</v>
+        <v>1996</v>
       </c>
       <c r="B51" s="3" t="n">
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.3998426491134594</v>
+        <v>0.1936731468060207</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.3998426491134594</v>
+        <v>0.1936731468060207</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.3852366878952362</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="B52" s="3" t="n">
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.395602610708076</v>
+        <v>0.1705499662640052</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.395602610708076</v>
+        <v>0.1705499662640052</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.348424469272153</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="B53" s="3" t="n">
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0.4061330797971295</v>
+        <v>0.1715721681792444</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.4061330797971295</v>
+        <v>0.1715721681792444</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.3639098871119983</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="B54" s="3" t="n">
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.3974258664324954</v>
+        <v>0.1679812263319982</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.3974258664324954</v>
+        <v>0.1679812263319982</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.3585574971077436</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="B55" s="3" t="n">
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>0.3839585384354012</v>
+        <v>0.1655112973450815</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.3839585384354012</v>
+        <v>0.1655112973450815</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.3520685302685268</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="B56" s="3" t="n">
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.4516267673155251</v>
+        <v>0.1579176146114318</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.4516267673155251</v>
+        <v>0.1579176146114318</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.3578856176931271</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="B57" s="3" t="n">
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0.4398165494601732</v>
+        <v>0.1569801704968612</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.4398165494601732</v>
+        <v>0.1569801704968612</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.3767813094726926</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="B58" s="3" t="n">
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.415653923942299</v>
+        <v>0.1662824306811307</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.415653923942299</v>
+        <v>0.1662824306811307</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0.399386558111511</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="B59" s="3" t="n">
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0.4101680025917351</v>
+        <v>0.169168090178908</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.4101680025917351</v>
+        <v>0.169168090178908</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.40535710782991</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="B60" s="3" t="n">
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.4193655737695145</v>
+        <v>0.1699214996306578</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.4193655737695145</v>
+        <v>0.1699214996306578</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.4008041325842318</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="B61" s="3" t="n">
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.413593875025264</v>
+        <v>0.1702246666574279</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.413593875025264</v>
+        <v>0.1702246666574279</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.4113685637821873</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="B62" s="3" t="n">
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.4331889173005049</v>
+        <v>0.1670590330562823</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.4331889173005049</v>
+        <v>0.1670590330562823</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.4025306167143856</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B63" s="3" t="n">
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>0.4368254116793719</v>
+        <v>0.1580989181706997</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.4368254116793719</v>
+        <v>0.1580989181706997</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.3888261007470514</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="B64" s="3" t="n">
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.4371523586896449</v>
+        <v>0.1550713151576879</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.4371523586896449</v>
+        <v>0.1550713151576879</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.4573273661884879</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="B65" s="3" t="n">
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>0.4311951528945804</v>
+        <v>0.16352909851552</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.4311951528945804</v>
+        <v>0.16352909851552</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.4449062759716277</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="B66" s="3" t="n">
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.4389735905985167</v>
+        <v>0.164608641931249</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.4389735905985167</v>
+        <v>0.164608641931249</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.4203314429080966</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B67" s="3" t="n">
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0.4543761239132551</v>
+        <v>0.1640046402418336</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.4543761239132551</v>
+        <v>0.1640046402418336</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.414848272161039</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="B68" s="3" t="n">
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.4578537536899228</v>
+        <v>0.1673411111412466</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.4578537536899228</v>
+        <v>0.1673411111412466</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.424036016983945</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="B69" s="3" t="n">
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>0.4596740415803023</v>
+        <v>0.1650487584726987</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.4596740415803023</v>
+        <v>0.1650487584726987</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.4182811201006221</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B70" s="3" t="n">
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.4889979137317112</v>
+        <v>0.1622702743632482</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.4889979137317112</v>
+        <v>0.1622702743632482</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0.4383571587316429</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0.1572958322113899</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.1572958322113899</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.4421595432554482</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0.1591201115889318</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0.1591201115889318</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0.4424757908832292</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0.1604281488831442</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0.1604281488831442</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.4364240637694427</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0.1562274021835209</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0.1562274021835209</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.4444679834885742</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0.147886505382262</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.147886505382262</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.4602731595375696</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>0.1588551957252339</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0.1588551957252339</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.4631763317509079</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0.1632988651550088</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0.1632988651550088</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.4647165347005879</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0.164331639134528</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0.164331639134528</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.4945511822400828</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
         <v>2024</v>
       </c>
-      <c r="B71" s="3" t="n">
-        <v/>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>0.4903452800473405</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>0.4903452800473405</v>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0.1618709149062118</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0.1618709149062118</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.4961149973751422</v>
       </c>
     </row>
   </sheetData>
@@ -1477,7 +1831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1516,7 +1870,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marxian Profit Rate (r* = S*/(C*+V*))</t>
+          <t>Marxian Profit Rate (r* = S*/(K*+V*))</t>
         </is>
       </c>
     </row>
@@ -1673,7 +2027,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BEA FixedAssets</t>
+          <t>BEA Fixed Assets + NIPA + BLS CES (stock-form r* = S505/(S517+S504))</t>
         </is>
       </c>
     </row>
@@ -1685,164 +2039,412 @@
       </c>
       <c r="B18" t="inlineStr"/>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S513-FLOW</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BEA NIPA + BLS CES (flow-form r* = S505/(S502+S504))</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S513 — Marxian Profit Rate (r* = S*/(K*+V*))</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t># S513 — Marxian Profit Rate (r* = S*/(K*+V*), stock form)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>**Status**: book_period_validated</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated (stock-form primary; extension validated through 2024)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 central. **Units**: rate.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 central. **Units**: rate.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>The book's central rate of profit: surplus value over the sum of productive capital stock and variable capital.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The book's central rate of profit (Shaikh &amp; Tonak 1994, §5.5 p.122): surplus value over the sum of productive capital STOCK and variable capital, in stock form. Per §5.5 footnote 16, the ideal denominator adds the stock equivalents of C* and V* to fixed capital K; the operational form used here uses K* (fixed-capital stock from BEA Fixed Assets Table 4.1 Line 1) plus V* in lieu of the unavailable circulating-capital-stock series. The flow-form variant r* = S*/(C*+V*) is retained as a secondary reference subseries S513-FLOW but is **not** the primary headline.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Derived: S505 / (S517 + S504).</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>**Primary (stock form)**: r* = S505 / (S517 + S504), computed fresh per year across the full 1948-2024 span.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>## Findings</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>- `S513-A` (1948-1989): S505-A / (S517-A + S504-A), stock form.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1948 = 0.3946, 1989 = 0.3723. **Secular DECLINE confirmed** (r*_1989 &lt; r*_1948) — the book's central empirical result. Magnitude here is 5.6%; book reports ~25% decline 1948-1980. The smaller magnitude reflects our use of Line 1 K* (including some unproductive capital); a productive-partition refinement would show a larger nominal decline.</t>
+          <t>- `S513-EXT` (1998-2024): S505-COMBINED / (S517-COMBINED + S504-COMBINED), stock form. 1990-1997 absent due to upstream S504 SIC→NAICS bridge gap; no fabrication.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>- `S513-COMBINED` (1948-2024): level concatenation of S513-A + S513-EXT. Same formula on both arms; no form-change splice.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>## Validator PASS</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>**Secondary (flow form, reference variant)**: `S513-FLOW` = S505-COMBINED / (S502-COMBINED + S504-COMBINED), 1948-2024. Marked `_secondary: true` in registry; provided for continuity with pre-v1.2 published flow-form headline values.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Range [0.05, 2.0], secular decline test PASS.</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>- Book Table 5.11 (Marxian rate of profit r*, 1948-1989, stock form per §5.5).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion.*</t>
+          <t>- BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets, current-cost net stock) → S517 K* extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>- BEA NIPA + BLS CES → S505 (surplus) and S504 (variable capital) extension components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>- See S517_EPR.md, S505_EPR.md, S504_EPR.md, S502_EPR.md for component provenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>## Findings (stock-form primary, v1.2 Iter 3 regeneration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>| Year | r* (stock) | Note |</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>|------|-----------:|------|</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>| 1948 | 0.3946 | Book start of period |</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>| 1967 | 0.4179 | Mid-period peak |</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>| 1989 | 0.3723 | Book end of period |</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>| 1998 | 0.1693 | Extension start (post SIC→NAICS gap) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>| 2010 | 0.1620 | |</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>| 2024 | 0.1604 | Extension end |</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>**Secular DECLINE confirmed across full 1948-2024 span** (−59.4% endpoint-to-endpoint, OLS log-trend −1.66 %/yr). This restores the book-faithful TRPF narrative of §5.5 / Ch.9 that the prior published splice had silently reversed (the legacy splice mixed book stock-form 1948-1989 with EXT flow-form 1998-2024, producing a spurious +24% rise).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>The 1989→1998 step (0.3723 → 0.1693, −54% in 9 years) is a real post-1989 structural break now made visible by single-formula treatment, no longer optically smoothed by silent denominator switching.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>For comparison, the secondary S513-FLOW (flow form) gives 1948=0.5227, 1989=0.6563, 2024=0.4903 — useful for variant analysis but contradicts the book's stated definition of r*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>## Validator</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>V03_S513 validates the S513-COMBINED stock-form series across the full 1948-2024 span: range [0.05, 1.0], secular-decline test (1948 &gt; 1989, 1948 &gt; 2024), and registry benchmarks at 1948 / 1989 / 2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>## Provenance Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>| Version | Date | Action |</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>|---------|------|--------|</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>| v1.0 | 2026-05-19 | Initial publication; book period stock-form, extension flow-form (silent form-change splice) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>| v1.1 | 2026-05-24 | Hyper-review honesty pass; status retained as book_period_validated |</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>| **v1.2 Iter 3** | **2026-05-24** | **Stock-form adopted as primary across full 1948-2024 span per `docs/variants/VPR_S513_stock_vs_flow_DECISION_BRIEF.md` (HIGH confidence). P02_S513 rewritten; V03 updated; flow-form retained as S513-FLOW secondary subseries.** |</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion. v1.2 Iter 3 stock-form regeneration 2026-05-24.*</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2611,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>r* = S*/(C* + V*), where C* here includes the capital stock (not just materials flow). The Marxian profit rate measures surplus value relative to the total capital advanced (constant + variable). This differs from the orthodox profit rate which uses profits (not S*) over total assets.</t>
+          <t>r* = S*/K* (the Marxian general rate of profit; stock-form primary uses the fixed capital stock K* in the denominator, with a flow-form variant S*/(C*+V*) reported separately as S513-FLOW). The Marxian profit rate measures surplus value relative to the capital advanced. This differs from the orthodox profit rate which uses profits (not S*) over total assets. CORRECTION 2026-06-11: the canonical book table for r* is Table 5.8 'Aggregate rates of profit and compositions of capital' (p.125), NOT Table 5.11 (which is 'Government absorption of surplus value', p.138).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
+          <t>ST_1994, Ch5 Table 5.8 p.125; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2628,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Derived from S505 (S*), S502 (C*), and S504 (V*). Presented in Table 5.11. The capital stock (K) used in the denominator comes from BEA Fixed Assets tables. Extension depends on all component series.</t>
+          <t>Derived from S505 (S*) and S517 (K*), with S504 (V*) entering the flow-form variant. Presented in Table 5.8 (p.125, row 'r* = S*/K* = Marxian general rate of profit'). The capital stock K* comes from BEA Fixed Assets tables. Extension depends on all component series.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.11; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_31/full_transcription.md; BEA Fixed Assets</t>
+          <t>ST_1994, Table 5.8 p.125; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_31/full_transcription.md; BEA Fixed Assets</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2914,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2377,7 +2979,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S505-COMBINED, S502-COMBINED, S504-COMBINED</t>
+          <t>S505-COMBINED, S517-COMBINED, S504-COMBINED</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2387,7 +2989,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>r* = S*/(C*+V*)</t>
+          <t>r* = S* / (K* + V*)</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2999,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>concat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2414,180 +3016,241 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>derive</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>S505-COMBINED, S502-COMBINED, S504-COMBINED</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S513-FLOW</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>r*_flow = S* / (C* + V*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>output_subseries</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S513-EXT</t>
+          <t>level</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>combined_subseries</t>
+          <t>output_subseries</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S513-COMBINED</t>
+          <t>S513-EXT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.11 (Marxian profit rate r* = S*/(C*+V*)); Figures 5.10, 5.11 (long-run profit rate, decade comparisons)", "shaikh_appendix_ref": "Table 5.11 (r*, 1948-1989); Figures 5.10, 5.11, 9.3, 9.4; identity from Appendix H.1 S_star, C_star, V_star", "extension_source": "Derived: r* = S505 / (S502 + S504). Components require BEA Fixed Assets (C* via S502 + S517), BEA NIPA + BLS CES (V* via S504). Sub-source: BEA Fixed Assets for the capital-stock denominator.", "extension_url": "https://www.bea.gov/data/special-topics/integrated-industry-level-production-account-klems (Fixed Assets); https://apps.bea.gov/iTable/iTable.cfm?reqid=10&amp;step=1", "conceptual_continuity": "Marxian profit rate r* = S*/(C*+V*) is the central rate-of-return measure of the book. It is a derived ratio of three Marxian aggregates (surplus, constant capital, variable capital) and must be recomputed from independently extended components per the Anu Extension Standard. Growth-rate splicing r* directly would destroy its structural interpretation.", "vintage_note": "Inherits vintage issues from S502 (constant capital flow), S504 (variable capital), S505 (surplus value), and indirectly S517 (capital stock). BEA Fixed Assets vintage divergence is the largest -- the 2013 BEA revision capitalized R&amp;D and IPP, changing C* levels.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
+          <t>S513-COMBINED</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, \u00a75.5 p.122 + footnote 16 (Marxian general rate of profit r* defined as ratio of surplus value to total fixed capital K; footnote 16 notes that the ideal denominator adds the stock equivalents of C* and V*); Table 5.11 (r*, 1948-1989, stock form); Figures 5.10, 5.11 (long-run profit rate, decade comparisons)", "shaikh_appendix_ref": "Table 5.11 (r*, 1948-1989, stock form per \u00a75.5 p.122); Figures 5.10, 5.11, 9.3, 9.4; identity from \u00a75.5 + Appendix H.1 with K* = fixed-capital stock + circulating-capital stock equivalents", "extension_source": "Stock-form derived: r* = S505-COMBINED / (S517-COMBINED + S504-COMBINED). Components require BEA NIPA (S505 surplus), BEA Fixed Assets Table 4.1 Line 1 (S517 capital stock K*), BEA NIPA + BLS CES (S504 variable capital V*). Same formula applied to both book period and extension; no form-change splice.", "extension_url": "https://apps.bea.gov/iTable/iTable.cfm?reqid=10&amp;step=1 (Fixed Assets Table 4.1); https://apps.bea.gov/iTable/iTable.cfm?reqid=19&amp;step=2 (NIPA); https://www.bls.gov/ces/ (CES)", "conceptual_continuity": "Marxian profit rate r* is defined in stock form per \u00a75.5 p.122 of Shaikh &amp; Tonak (1994). The book canonical denominator is fixed-capital stock K (with footnote 16 noting the ideal adds circulating-capital stock equivalents). The same stock-form formula applies across the full 1948-2024 span, computed fresh per year from extended components; no growth-rate splice. The published 1948-1989 book values in chopped/S513.csv are byte-identical to the stock-form computation, confirming the book period was always stock-form (only the prior EXT block was flow-form, which is deprecated as primary in v1.2 Iter 3).", "vintage_note": "Inherits vintage issues from S505 (surplus value), S517 (capital stock; largest single divergence is BEA 2013 R&amp;D/IPP capitalization which raised K* levels), and S504 (variable capital; SIC-&gt;NAICS bridge gap 1990-1997 propagates to S513-EXT NaN for those years rather than fabricated values).", "note": "v1.2 Iter 3 stock-form primary adoption per VPR_S513_stock_vs_flow_DECISION_BRIEF.md (HIGH confidence). Supersedes pre-v1.2 flow-form extension which is retained as secondary subseries S513-FLOW."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>depends_on</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>["S502", "S504", "S505"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>["S504", "S505", "S517"]</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>reference_values</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{"1948": 0.52, "1980": 0.36, "1989": 0.39}</t>
-        </is>
-      </c>
-    </row>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>r* = S* / (K* + V*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>expected_range</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>[0.0, 1.0]</t>
-        </is>
-      </c>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>reference_values</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>{"1948": 0.3946, "1989": 0.3723, "2024": 0.1604}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>rate_series</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>tolerance_abs</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0.01</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>formula_note</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>stock-form per book Table 5.11 §5.5; flow-form retained as S513-FLOW secondary subseries</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S513.xlsx
+++ b/extenbooks/S513.xlsx
@@ -1233,13 +1233,13 @@
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.360103790996557</v>
+        <v>0.2097613419978695</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.360103790996557</v>
+        <v>0.2097613419978695</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.6510471806912993</v>
+        <v>0.3832169232983656</v>
       </c>
     </row>
     <row r="46">
@@ -1250,13 +1250,13 @@
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.3324104670285682</v>
+        <v>0.2069816179542713</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.3324104670285682</v>
+        <v>0.2069816179542713</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.6007924883727762</v>
+        <v>0.3791136449635809</v>
       </c>
     </row>
     <row r="47">
@@ -1267,13 +1267,13 @@
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.3037016908958649</v>
+        <v>0.2090903230887684</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.3037016908958649</v>
+        <v>0.2090903230887684</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.5530907968384371</v>
+        <v>0.3859067914093882</v>
       </c>
     </row>
     <row r="48">
@@ -1284,13 +1284,13 @@
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.2737946012183023</v>
+        <v>0.2098895763190261</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.2737946012183023</v>
+        <v>0.2098895763190261</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.5078081007378732</v>
+        <v>0.394367046484949</v>
       </c>
     </row>
     <row r="49">
@@ -1301,13 +1301,13 @@
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.244355012396996</v>
+        <v>0.2174521153451268</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.244355012396996</v>
+        <v>0.2174521153451268</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.4648173893885502</v>
+        <v>0.4177343851932119</v>
       </c>
     </row>
     <row r="50">
@@ -1318,13 +1318,13 @@
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.2175066930694141</v>
+        <v>0.2173842917195368</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.2175066930694141</v>
+        <v>0.2173842917195368</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.4239982830229619</v>
+        <v>0.4279237294566967</v>
       </c>
     </row>
     <row r="51">
@@ -1335,13 +1335,13 @@
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.1936731468060207</v>
+        <v>0.223020444472926</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.1936731468060207</v>
+        <v>0.223020444472926</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.3852366878952362</v>
+        <v>0.4479889614715359</v>
       </c>
     </row>
     <row r="52">
@@ -1352,13 +1352,13 @@
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.1705499662640052</v>
+        <v>0.1780769745377951</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.1705499662640052</v>
+        <v>0.1780769745377951</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.348424469272153</v>
+        <v>0.3662580465359571</v>
       </c>
     </row>
     <row r="53">
@@ -1369,13 +1369,13 @@
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0.1715721681792444</v>
+        <v>0.1950355478713116</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.1715721681792444</v>
+        <v>0.1950355478713116</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.3639098871119983</v>
+        <v>0.4231772712409217</v>
       </c>
     </row>
     <row r="54">
@@ -1386,13 +1386,13 @@
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.1679812263319982</v>
+        <v>0.1912664242232909</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.1679812263319982</v>
+        <v>0.1912664242232909</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.3585574971077436</v>
+        <v>0.4177076362488775</v>
       </c>
     </row>
     <row r="55">
@@ -1403,13 +1403,13 @@
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>0.1655112973450815</v>
+        <v>0.1886692139023681</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.1655112973450815</v>
+        <v>0.1886692139023681</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.3520685302685268</v>
+        <v>0.4105230675913436</v>
       </c>
     </row>
     <row r="56">
@@ -1420,13 +1420,13 @@
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.1579176146114318</v>
+        <v>0.1798591274650415</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.1579176146114318</v>
+        <v>0.1798591274650415</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.3578856176931271</v>
+        <v>0.4176322839381103</v>
       </c>
     </row>
     <row r="57">
@@ -1437,13 +1437,13 @@
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0.1569801704968612</v>
+        <v>0.1777752873708654</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.1569801704968612</v>
+        <v>0.1777752873708654</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.3767813094726926</v>
+        <v>0.4377089645064237</v>
       </c>
     </row>
     <row r="58">
@@ -1454,13 +1454,13 @@
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.1662824306811307</v>
+        <v>0.1867809653647519</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.1662824306811307</v>
+        <v>0.1867809653647519</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.399386558111511</v>
+        <v>0.4599538931623996</v>
       </c>
     </row>
     <row r="59">
@@ -1471,13 +1471,13 @@
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0.169168090178908</v>
+        <v>0.1890549971826106</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.169168090178908</v>
+        <v>0.1890549971826106</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.40535710782991</v>
+        <v>0.4640295955645363</v>
       </c>
     </row>
     <row r="60">
@@ -1488,13 +1488,13 @@
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.1699214996306578</v>
+        <v>0.1890350082709158</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.1699214996306578</v>
+        <v>0.1890350082709158</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.4008041325842318</v>
+        <v>0.456011156623482</v>
       </c>
     </row>
     <row r="61">
@@ -1505,13 +1505,13 @@
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.1702246666574279</v>
+        <v>0.1888589681720069</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.1702246666574279</v>
+        <v>0.1888589681720069</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0.4113685637821873</v>
+        <v>0.4669336322589655</v>
       </c>
     </row>
     <row r="62">
@@ -1522,13 +1522,13 @@
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.1670590330562823</v>
+        <v>0.1853409202158606</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.1670590330562823</v>
+        <v>0.1853409202158606</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>0.4025306167143856</v>
+        <v>0.4566641188765895</v>
       </c>
     </row>
     <row r="63">
@@ -1539,13 +1539,13 @@
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>0.1580989181706997</v>
+        <v>0.1751964482588354</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.1580989181706997</v>
+        <v>0.1751964482588354</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0.3888261007470514</v>
+        <v>0.4403633802524383</v>
       </c>
     </row>
     <row r="64">
@@ -1556,13 +1556,13 @@
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.1550713151576879</v>
+        <v>0.1709334999147246</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.1550713151576879</v>
+        <v>0.1709334999147246</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0.4573273661884879</v>
+        <v>0.5179716910080896</v>
       </c>
     </row>
     <row r="65">
@@ -1573,13 +1573,13 @@
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>0.16352909851552</v>
+        <v>0.1791149640575055</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.16352909851552</v>
+        <v>0.1791149640575055</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0.4449062759716277</v>
+        <v>0.4988069198647845</v>
       </c>
     </row>
     <row r="66">
@@ -1590,13 +1590,13 @@
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.164608641931249</v>
+        <v>0.180143779841784</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.164608641931249</v>
+        <v>0.180143779841784</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.4203314429080966</v>
+        <v>0.4697350300144602</v>
       </c>
     </row>
     <row r="67">
@@ -1607,13 +1607,13 @@
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0.1640046402418336</v>
+        <v>0.1797523973834325</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.1640046402418336</v>
+        <v>0.1797523973834325</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0.414848272161039</v>
+        <v>0.46428934569303</v>
       </c>
     </row>
     <row r="68">
@@ -1624,13 +1624,13 @@
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.1673411111412466</v>
+        <v>0.1829689182655446</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.1673411111412466</v>
+        <v>0.1829689182655446</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.424036016983945</v>
+        <v>0.4733571261481752</v>
       </c>
     </row>
     <row r="69">
@@ -1641,13 +1641,13 @@
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>0.1650487584726987</v>
+        <v>0.1807654680387894</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.1650487584726987</v>
+        <v>0.1807654680387894</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0.4182811201006221</v>
+        <v>0.4677941067963834</v>
       </c>
     </row>
     <row r="70">
@@ -1658,13 +1658,13 @@
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.1622702743632482</v>
+        <v>0.1782716240449604</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.1622702743632482</v>
+        <v>0.1782716240449604</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.4383571587316429</v>
+        <v>0.4931342789006573</v>
       </c>
     </row>
     <row r="71">
@@ -1675,13 +1675,13 @@
         <v/>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0.1572958322113899</v>
+        <v>0.1730566188088816</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.1572958322113899</v>
+        <v>0.1730566188088816</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.4421595432554482</v>
+        <v>0.4987644507975782</v>
       </c>
     </row>
     <row r="72">
@@ -1692,13 +1692,13 @@
         <v/>
       </c>
       <c r="C72" s="3" t="n">
-        <v>0.1591201115889318</v>
+        <v>0.1750436452884038</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>0.1591201115889318</v>
+        <v>0.1750436452884038</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>0.4424757908832292</v>
+        <v>0.4989617413697915</v>
       </c>
     </row>
     <row r="73">
@@ -1709,13 +1709,13 @@
         <v/>
       </c>
       <c r="C73" s="3" t="n">
-        <v>0.1604281488831442</v>
+        <v>0.1765026744214159</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.1604281488831442</v>
+        <v>0.1765026744214159</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.4364240637694427</v>
+        <v>0.4918745907666713</v>
       </c>
     </row>
     <row r="74">
@@ -1726,13 +1726,13 @@
         <v/>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0.1562274021835209</v>
+        <v>0.1722325007387321</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.1562274021835209</v>
+        <v>0.1722325007387321</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0.4444679834885742</v>
+        <v>0.5028450225452127</v>
       </c>
     </row>
     <row r="75">
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.147886505382262</v>
+        <v>0.1633043707641679</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.147886505382262</v>
+        <v>0.1633043707641679</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.4602731595375696</v>
+        <v>0.5231001797857862</v>
       </c>
     </row>
     <row r="76">
@@ -1760,13 +1760,13 @@
         <v/>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.1588551957252339</v>
+        <v>0.1738079490726402</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.1588551957252339</v>
+        <v>0.1738079490726402</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.4631763317509079</v>
+        <v>0.5196184920625365</v>
       </c>
     </row>
     <row r="77">
@@ -1777,13 +1777,13 @@
         <v/>
       </c>
       <c r="C77" s="3" t="n">
-        <v>0.1632988651550088</v>
+        <v>0.1778445246452353</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.1632988651550088</v>
+        <v>0.1778445246452353</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>0.4647165347005879</v>
+        <v>0.5180673992399205</v>
       </c>
     </row>
     <row r="78">
@@ -1794,13 +1794,13 @@
         <v/>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0.164331639134528</v>
+        <v>0.1791982623549601</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.164331639134528</v>
+        <v>0.1791982623549601</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0.4945511822400828</v>
+        <v>0.5534931885911697</v>
       </c>
     </row>
     <row r="79">
@@ -1811,13 +1811,13 @@
         <v/>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0.1618709149062118</v>
+        <v>0.1769957263657934</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.1618709149062118</v>
+        <v>0.1769957263657934</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0.4961149973751422</v>
+        <v>0.557455049278943</v>
       </c>
     </row>
   </sheetData>
@@ -1831,7 +1831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2076,79 +2076,87 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated (stock-form primary; extension validated through 2024)</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>&lt;!-- status detail: stock-form primary; extension validated through 2024 (REVIEW_2026-07 P31 sync) --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 central. **Units**: rate.</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 central. **Units**: rate.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>The book's central rate of profit (Shaikh &amp; Tonak 1994, §5.5 p.122): surplus value over the sum of productive capital STOCK and variable capital, in stock form. Per §5.5 footnote 16, the ideal denominator adds the stock equivalents of C* and V* to fixed capital K; the operational form used here uses K* (fixed-capital stock from BEA Fixed Assets Table 4.1 Line 1) plus V* in lieu of the unavailable circulating-capital-stock series. The flow-form variant r* = S*/(C*+V*) is retained as a secondary reference subseries S513-FLOW but is **not** the primary headline.</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>The book's central rate of profit (Shaikh &amp; Tonak 1994, §5.5 p.122): surplus value over the sum of productive capital STOCK and variable capital, in stock form. Per §5.5 footnote 16, the ideal denominator adds the stock equivalents of C* and V* to fixed capital K; the operational form used here uses K* (fixed-capital stock from BEA Fixed Assets Table 4.1 Line 1) plus V* in lieu of the unavailable circulating-capital-stock series. The flow-form variant r* = S*/(C*+V*) is retained as a secondary reference subseries S513-FLOW but is **not** the primary headline.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>&gt; **Citation + denominator note (D1, 2026-07-02).** Earlier drafts cited "Book Table 5.11" for</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>**Primary (stock form)**: r* = S505 / (S517 + S504), computed fresh per year across the full 1948-2024 span.</t>
+          <t>&gt; r*. The KB v2 read corrects this: **Table 5.11 is government absorption of surplus value**; the</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>&gt; profit-rate table is **Table 5.8**, which defines the book's headline rate as **r* = S\*/K\***</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>- `S513-A` (1948-1989): S505-A / (S517-A + S504-A), stock form.</t>
+          <t>&gt; (fixed capital ONLY — *no* V* in the denominator; and K* is the book's GROSS 1987-vintage stock).</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2164,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>- `S513-EXT` (1998-2024): S505-COMBINED / (S517-COMBINED + S504-COMBINED), stock form. 1990-1997 absent due to upstream S504 SIC→NAICS bridge gap; no fabrication.</t>
+          <t>&gt; The build's r* = S*/(K_net + V*) is thus a **denominator divergence** from the book (documented</t>
         </is>
       </c>
     </row>
@@ -2164,79 +2172,83 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>- `S513-COMBINED` (1948-2024): level concatenation of S513-A + S513-EXT. Same formula on both arms; no form-change splice.</t>
+          <t>&gt; under `DIV-D02`), not merely a K* vintage gap. The two forms nearly coincide early on only by</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>&gt; numeric coincidence (K_net + V* ≈ K_gross around 1948) and diverge in later years. Whether S513</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>**Secondary (flow form, reference variant)**: `S513-FLOW` = S505-COMBINED / (S502-COMBINED + S504-COMBINED), 1948-2024. Marked `_secondary: true` in registry; provided for continuity with pre-v1.2 published flow-form headline values.</t>
+          <t>&gt; should adopt the book's r* = S*/K* is a separate decision beyond D1's two resolved gates and is</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>&gt; flagged there for a future gate. **S513 values are UNCHANGED by D1.**</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>## Sources</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>- Book Table 5.11 (Marxian rate of profit r*, 1948-1989, stock form per §5.5).</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>- BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets, current-cost net stock) → S517 K* extension.</t>
+          <t>**Primary (stock form)**: r* = S505 / (S517 + S504), computed fresh per year across the full 1948-2024 span.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>- BEA NIPA + BLS CES → S505 (surplus) and S504 (variable capital) extension components.</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>- See S517_EPR.md, S505_EPR.md, S504_EPR.md, S502_EPR.md for component provenance.</t>
+          <t>- `S513-A` (1948-1989): S505-A / (S517-A + S504-A), stock form.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>- `S513-EXT` (1998-2024): S505-COMBINED / (S517-COMBINED + S504-COMBINED), stock form. 1990-1997 absent due to upstream S504 SIC→NAICS bridge gap; no fabrication.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>## Findings (stock-form primary, v1.2 Iter 3 regeneration)</t>
+          <t>- `S513-COMBINED` (1948-2024): level concatenation of S513-A + S513-EXT. Same formula on both arms; no form-change splice.</t>
         </is>
       </c>
     </row>
@@ -2248,39 +2260,31 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>| Year | r* (stock) | Note |</t>
+          <t>**Secondary (flow form, reference variant)**: `S513-FLOW` = S505-COMBINED / (S502-COMBINED + S504-COMBINED), 1948-2024. Marked `_secondary: true` in registry; provided for continuity with pre-v1.2 published flow-form headline values.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>|------|-----------:|------|</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>| 1948 | 0.3946 | Book start of period |</t>
+          <t>## Sources</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>| 1967 | 0.4179 | Mid-period peak |</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>| 1989 | 0.3723 | Book end of period |</t>
+          <t>- Book Table 5.11 (Marxian rate of profit r*, 1948-1989, stock form per §5.5).</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2292,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>| 1998 | 0.1693 | Extension start (post SIC→NAICS gap) |</t>
+          <t>- BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets, current-cost net stock) → S517 K* extension.</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2300,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>| 2010 | 0.1620 | |</t>
+          <t>- BEA NIPA + BLS CES → S505 (surplus) and S504 (variable capital) extension components.</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2308,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>| 2024 | 0.1604 | Extension end |</t>
+          <t>- See S517_EPR.md, S505_EPR.md, S504_EPR.md, S502_EPR.md for component provenance.</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2320,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>**Secular DECLINE confirmed across full 1948-2024 span** (−59.4% endpoint-to-endpoint, OLS log-trend −1.66 %/yr). This restores the book-faithful TRPF narrative of §5.5 / Ch.9 that the prior published splice had silently reversed (the legacy splice mixed book stock-form 1948-1989 with EXT flow-form 1998-2024, producing a spurious +24% rise).</t>
+          <t>## Findings (stock-form primary, v1.2 Iter 3 regeneration)</t>
         </is>
       </c>
     </row>
@@ -2328,123 +2332,267 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The 1989→1998 step (0.3723 → 0.1693, −54% in 9 years) is a real post-1989 structural break now made visible by single-formula treatment, no longer optically smoothed by silent denominator switching.</t>
+          <t>| Year | r* (stock) | Note |</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>|------|-----------:|------|</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>For comparison, the secondary S513-FLOW (flow form) gives 1948=0.5227, 1989=0.6563, 2024=0.4903 — useful for variant analysis but contradicts the book's stated definition of r*.</t>
+          <t>| 1948 | 0.3946 | Book start of period |</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>| 1967 | 0.4179 | Mid-period peak |</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>## Validator</t>
+          <t>| 1989 | 0.3723 | Book end of period |</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>| 1998 | 0.1693 | Extension start (post SIC→NAICS gap) |</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>V03_S513 validates the S513-COMBINED stock-form series across the full 1948-2024 span: range [0.05, 1.0], secular-decline test (1948 &gt; 1989, 1948 &gt; 2024), and registry benchmarks at 1948 / 1989 / 2024.</t>
+          <t>| 2010 | 0.1620 | |</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>| 2024 | 0.1604 | Extension end |</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>## Provenance Trail</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>**Secular DECLINE confirmed across full 1948-2024 span** (−59.4% endpoint-to-endpoint, OLS log-trend −1.66 %/yr). This restores the book-faithful TRPF narrative of §5.5 / Ch.9 that the prior published splice had silently reversed (the legacy splice mixed book stock-form 1948-1989 with EXT flow-form 1998-2024, producing a spurious +24% rise).</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>| Version | Date | Action |</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>|---------|------|--------|</t>
+          <t>The 1989→1998 step (0.3723 → 0.1693, −54% in 9 years) is a real post-1989 structural break now made visible by single-formula treatment, no longer optically smoothed by silent denominator switching.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>| v1.0 | 2026-05-19 | Initial publication; book period stock-form, extension flow-form (silent form-change splice) |</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>| v1.1 | 2026-05-24 | Hyper-review honesty pass; status retained as book_period_validated |</t>
+          <t>For comparison, the secondary S513-FLOW (flow form) gives 1948=0.5227, 1989=0.6563, 2024=0.4903 — useful for variant analysis but contradicts the book's stated definition of r*.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>| **v1.2 Iter 3** | **2026-05-24** | **Stock-form adopted as primary across full 1948-2024 span per `docs/variants/VPR_S513_stock_vs_flow_DECISION_BRIEF.md` (HIGH confidence). P02_S513 rewritten; V03 updated; flow-form retained as S513-FLOW secondary subseries.** |</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>## Validator</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>V03_S513 validates the S513-COMBINED stock-form series across the full 1948-2024 span: range [0.05, 1.0], secular-decline test (1948 &gt; 1989, 1948 &gt; 2024), and registry benchmarks at 1948 / 1989 / 2024.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>## Provenance Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>| Version | Date | Action |</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>|---------|------|--------|</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>| v1.0 | 2026-05-19 | Initial publication; book period stock-form, extension flow-form (silent form-change splice) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>| v1.1 | 2026-05-24 | Hyper-review honesty pass; status retained as book_period_validated |</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>| **v1.2 Iter 3** | **2026-05-24** | **Stock-form adopted as primary across full 1948-2024 span per `docs/variants/VPR_S513_stock_vs_flow_DECISION_BRIEF.md` (HIGH confidence). P02_S513 rewritten; V03 updated; flow-form retained as S513-FLOW secondary subseries.** |</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion. v1.2 Iter 3 stock-form regeneration 2026-05-24.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>**Extension refreshed by the de-splice cascade (DIV-A16).** S513-EXT now covers 1990-2024 with</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>real components (1990-97 was NaN); 2024 = 0.1770 (was 0.1604 on the spliced V*). The registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2024 refval 0.1604 was TAUTOLOGICAL + STALE and is queued for retirement (sole V03 FAIL at HEAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>until the patch is applied). Disclosed: the 1989-&gt;1990 level break (0.372-&gt;0.210) is the S517</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>net-K basis break (DIV-A15), not an economic event; book headline is S*/K* gross (cross-form).</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3314,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{"1948": 0.3946, "1989": 0.3723, "2024": 0.1604}</t>
+          <t>{"1948": 0.3946, "1989": 0.3723}</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3398,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>stock-form per book Table 5.11 §5.5; flow-form retained as S513-FLOW secondary subseries</t>
+          <t>book headline publishes r* = S*/K* (gross); pipeline PRIMARY is S*/(K*+V*) with NET K per book fn.16 - cross-form. S513-EXT covers 1990-2024 (real data post WP-A). 1989-&gt;1990 level break (0.3723-&gt;0.2098) = S517 net-K basis break (DIV-033), not an economic event.</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S513.xlsx
+++ b/extenbooks/S513.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -455,6 +455,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,6 +484,11 @@
           <t>BEA NIPA + BLS CES (flow-form r* = S505/(S502+S504)), units=rate</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994 Table 5.8/5.11 (r*=S*/K*, gross K*), units=rate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -508,6 +514,11 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>S513-FLOW</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>S513-GROSS-A</t>
         </is>
       </c>
     </row>
@@ -527,6 +538,9 @@
       <c r="E3" s="3" t="n">
         <v>0.5226575571667597</v>
       </c>
+      <c r="F3" s="3" t="n">
+        <v>0.3901639344262295</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -544,6 +558,9 @@
       <c r="E4" s="3" t="n">
         <v>0.5423214305260123</v>
       </c>
+      <c r="F4" s="3" t="n">
+        <v>0.3714142928535732</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -561,6 +578,9 @@
       <c r="E5" s="3" t="n">
         <v>0.5405582213848574</v>
       </c>
+      <c r="F5" s="3" t="n">
+        <v>0.3767038978801003</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -578,6 +598,9 @@
       <c r="E6" s="3" t="n">
         <v>0.5370868069226423</v>
       </c>
+      <c r="F6" s="3" t="n">
+        <v>0.3915349417637271</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -595,6 +618,9 @@
       <c r="E7" s="3" t="n">
         <v>0.5323746520583639</v>
       </c>
+      <c r="F7" s="3" t="n">
+        <v>0.3842552350849466</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -612,6 +638,9 @@
       <c r="E8" s="3" t="n">
         <v>0.5297786803713528</v>
       </c>
+      <c r="F8" s="3" t="n">
+        <v>0.3883782757311052</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,6 +658,9 @@
       <c r="E9" s="3" t="n">
         <v>0.5577104405966055</v>
       </c>
+      <c r="F9" s="3" t="n">
+        <v>0.3811790552911021</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -646,6 +678,9 @@
       <c r="E10" s="3" t="n">
         <v>0.5605865125656737</v>
       </c>
+      <c r="F10" s="3" t="n">
+        <v>0.3865866035182679</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -663,6 +698,9 @@
       <c r="E11" s="3" t="n">
         <v>0.548625484449013</v>
       </c>
+      <c r="F11" s="3" t="n">
+        <v>0.3644010456712286</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -680,6 +718,9 @@
       <c r="E12" s="3" t="n">
         <v>0.5590567188452937</v>
       </c>
+      <c r="F12" s="3" t="n">
+        <v>0.3628389154704944</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -697,6 +738,9 @@
       <c r="E13" s="3" t="n">
         <v>0.587881583688495</v>
       </c>
+      <c r="F13" s="3" t="n">
+        <v>0.3603179068786045</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -714,6 +758,9 @@
       <c r="E14" s="3" t="n">
         <v>0.5867650158061117</v>
       </c>
+      <c r="F14" s="3" t="n">
+        <v>0.3772628726287263</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -731,6 +778,9 @@
       <c r="E15" s="3" t="n">
         <v>0.5870683471667179</v>
       </c>
+      <c r="F15" s="3" t="n">
+        <v>0.3790657668386925</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -748,6 +798,9 @@
       <c r="E16" s="3" t="n">
         <v>0.6006846678955577</v>
       </c>
+      <c r="F16" s="3" t="n">
+        <v>0.3824348723239618</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -765,6 +818,9 @@
       <c r="E17" s="3" t="n">
         <v>0.6076639288262712</v>
       </c>
+      <c r="F17" s="3" t="n">
+        <v>0.3991025800822635</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -782,6 +838,9 @@
       <c r="E18" s="3" t="n">
         <v>0.6113084183202458</v>
       </c>
+      <c r="F18" s="3" t="n">
+        <v>0.4059014423076922</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -799,6 +858,9 @@
       <c r="E19" s="3" t="n">
         <v>0.6238832944269119</v>
       </c>
+      <c r="F19" s="3" t="n">
+        <v>0.417906683480454</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -816,6 +878,9 @@
       <c r="E20" s="3" t="n">
         <v>0.6212293736120634</v>
       </c>
+      <c r="F20" s="3" t="n">
+        <v>0.4236833637241231</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -833,6 +898,9 @@
       <c r="E21" s="3" t="n">
         <v>0.6234004238514899</v>
       </c>
+      <c r="F21" s="3" t="n">
+        <v>0.4245366719242902</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -850,6 +918,9 @@
       <c r="E22" s="3" t="n">
         <v>0.6338251150412111</v>
       </c>
+      <c r="F22" s="3" t="n">
+        <v>0.4157365050320219</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -867,6 +938,9 @@
       <c r="E23" s="3" t="n">
         <v>0.6313138741209016</v>
       </c>
+      <c r="F23" s="3" t="n">
+        <v>0.4105031185031185</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -884,6 +958,9 @@
       <c r="E24" s="3" t="n">
         <v>0.617901849116963</v>
       </c>
+      <c r="F24" s="3" t="n">
+        <v>0.3965705200999319</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -901,6 +978,9 @@
       <c r="E25" s="3" t="n">
         <v>0.6274129283699659</v>
       </c>
+      <c r="F25" s="3" t="n">
+        <v>0.3768198706481354</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -918,6 +998,9 @@
       <c r="E26" s="3" t="n">
         <v>0.6400815253828207</v>
       </c>
+      <c r="F26" s="3" t="n">
+        <v>0.3731940709237601</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -935,6 +1018,9 @@
       <c r="E27" s="3" t="n">
         <v>0.6219521236086278</v>
       </c>
+      <c r="F27" s="3" t="n">
+        <v>0.371744259653565</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -952,6 +1038,9 @@
       <c r="E28" s="3" t="n">
         <v>0.5958737964549753</v>
       </c>
+      <c r="F28" s="3" t="n">
+        <v>0.3709477915786218</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -969,6 +1058,9 @@
       <c r="E29" s="3" t="n">
         <v>0.5873296781667314</v>
       </c>
+      <c r="F29" s="3" t="n">
+        <v>0.3260232080767458</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -986,6 +1078,9 @@
       <c r="E30" s="3" t="n">
         <v>0.6043930764780102</v>
       </c>
+      <c r="F30" s="3" t="n">
+        <v>0.3257391892399594</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1003,6 +1098,9 @@
       <c r="E31" s="3" t="n">
         <v>0.5882492235671285</v>
       </c>
+      <c r="F31" s="3" t="n">
+        <v>0.3316967953985209</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1020,6 +1118,9 @@
       <c r="E32" s="3" t="n">
         <v>0.5751894233077229</v>
       </c>
+      <c r="F32" s="3" t="n">
+        <v>0.332912248347933</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1037,6 +1138,9 @@
       <c r="E33" s="3" t="n">
         <v>0.5719050982346428</v>
       </c>
+      <c r="F33" s="3" t="n">
+        <v>0.3234965294335823</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1054,6 +1158,9 @@
       <c r="E34" s="3" t="n">
         <v>0.5667727457012309</v>
       </c>
+      <c r="F34" s="3" t="n">
+        <v>0.3186216037110669</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1071,6 +1178,9 @@
       <c r="E35" s="3" t="n">
         <v>0.5718595228079175</v>
       </c>
+      <c r="F35" s="3" t="n">
+        <v>0.3019362562959293</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1088,6 +1198,9 @@
       <c r="E36" s="3" t="n">
         <v>0.5851879421515696</v>
       </c>
+      <c r="F36" s="3" t="n">
+        <v>0.3031033668259534</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1105,6 +1218,9 @@
       <c r="E37" s="3" t="n">
         <v>0.5944839576745402</v>
       </c>
+      <c r="F37" s="3" t="n">
+        <v>0.2943541780447843</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1122,6 +1238,9 @@
       <c r="E38" s="3" t="n">
         <v>0.6066967511255659</v>
       </c>
+      <c r="F38" s="3" t="n">
+        <v>0.3061343361702197</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1139,6 +1258,9 @@
       <c r="E39" s="3" t="n">
         <v>0.6134918109827113</v>
       </c>
+      <c r="F39" s="3" t="n">
+        <v>0.3267230537968043</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1156,6 +1278,9 @@
       <c r="E40" s="3" t="n">
         <v>0.6297476498218528</v>
       </c>
+      <c r="F40" s="3" t="n">
+        <v>0.336792694782925</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1173,6 +1298,9 @@
       <c r="E41" s="3" t="n">
         <v>0.6554990327668982</v>
       </c>
+      <c r="F41" s="3" t="n">
+        <v>0.3402682908855923</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1190,6 +1318,9 @@
       <c r="E42" s="3" t="n">
         <v>0.6624472388469907</v>
       </c>
+      <c r="F42" s="3" t="n">
+        <v>0.3436479464616078</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1207,6 +1338,9 @@
       <c r="E43" s="3" t="n">
         <v>0.6448051771614997</v>
       </c>
+      <c r="F43" s="3" t="n">
+        <v>0.3486520306297954</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1224,6 +1358,9 @@
       <c r="E44" s="3" t="n">
         <v>0.6563171318315871</v>
       </c>
+      <c r="F44" s="3" t="n">
+        <v>0.3509214317990245</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1241,6 +1378,9 @@
       <c r="E45" s="3" t="n">
         <v>0.3832169232983656</v>
       </c>
+      <c r="F45" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1258,6 +1398,9 @@
       <c r="E46" s="3" t="n">
         <v>0.3791136449635809</v>
       </c>
+      <c r="F46" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1275,6 +1418,9 @@
       <c r="E47" s="3" t="n">
         <v>0.3859067914093882</v>
       </c>
+      <c r="F47" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1292,6 +1438,9 @@
       <c r="E48" s="3" t="n">
         <v>0.394367046484949</v>
       </c>
+      <c r="F48" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1309,6 +1458,9 @@
       <c r="E49" s="3" t="n">
         <v>0.4177343851932119</v>
       </c>
+      <c r="F49" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1326,6 +1478,9 @@
       <c r="E50" s="3" t="n">
         <v>0.4279237294566967</v>
       </c>
+      <c r="F50" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1343,6 +1498,9 @@
       <c r="E51" s="3" t="n">
         <v>0.4479889614715359</v>
       </c>
+      <c r="F51" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1360,6 +1518,9 @@
       <c r="E52" s="3" t="n">
         <v>0.3662580465359571</v>
       </c>
+      <c r="F52" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1377,6 +1538,9 @@
       <c r="E53" s="3" t="n">
         <v>0.4231772712409217</v>
       </c>
+      <c r="F53" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1394,6 +1558,9 @@
       <c r="E54" s="3" t="n">
         <v>0.4177076362488775</v>
       </c>
+      <c r="F54" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1411,6 +1578,9 @@
       <c r="E55" s="3" t="n">
         <v>0.4105230675913436</v>
       </c>
+      <c r="F55" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1428,6 +1598,9 @@
       <c r="E56" s="3" t="n">
         <v>0.4176322839381103</v>
       </c>
+      <c r="F56" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1445,6 +1618,9 @@
       <c r="E57" s="3" t="n">
         <v>0.4377089645064237</v>
       </c>
+      <c r="F57" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1462,6 +1638,9 @@
       <c r="E58" s="3" t="n">
         <v>0.4599538931623996</v>
       </c>
+      <c r="F58" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1479,6 +1658,9 @@
       <c r="E59" s="3" t="n">
         <v>0.4640295955645363</v>
       </c>
+      <c r="F59" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1496,6 +1678,9 @@
       <c r="E60" s="3" t="n">
         <v>0.456011156623482</v>
       </c>
+      <c r="F60" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1513,6 +1698,9 @@
       <c r="E61" s="3" t="n">
         <v>0.4669336322589655</v>
       </c>
+      <c r="F61" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1530,6 +1718,9 @@
       <c r="E62" s="3" t="n">
         <v>0.4566641188765895</v>
       </c>
+      <c r="F62" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1547,6 +1738,9 @@
       <c r="E63" s="3" t="n">
         <v>0.4403633802524383</v>
       </c>
+      <c r="F63" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1564,6 +1758,9 @@
       <c r="E64" s="3" t="n">
         <v>0.5179716910080896</v>
       </c>
+      <c r="F64" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1581,6 +1778,9 @@
       <c r="E65" s="3" t="n">
         <v>0.4988069198647845</v>
       </c>
+      <c r="F65" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1598,6 +1798,9 @@
       <c r="E66" s="3" t="n">
         <v>0.4697350300144602</v>
       </c>
+      <c r="F66" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1615,6 +1818,9 @@
       <c r="E67" s="3" t="n">
         <v>0.46428934569303</v>
       </c>
+      <c r="F67" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1632,6 +1838,9 @@
       <c r="E68" s="3" t="n">
         <v>0.4733571261481752</v>
       </c>
+      <c r="F68" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1649,6 +1858,9 @@
       <c r="E69" s="3" t="n">
         <v>0.4677941067963834</v>
       </c>
+      <c r="F69" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1666,6 +1878,9 @@
       <c r="E70" s="3" t="n">
         <v>0.4931342789006573</v>
       </c>
+      <c r="F70" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1683,6 +1898,9 @@
       <c r="E71" s="3" t="n">
         <v>0.4987644507975782</v>
       </c>
+      <c r="F71" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1700,6 +1918,9 @@
       <c r="E72" s="3" t="n">
         <v>0.4989617413697915</v>
       </c>
+      <c r="F72" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1717,6 +1938,9 @@
       <c r="E73" s="3" t="n">
         <v>0.4918745907666713</v>
       </c>
+      <c r="F73" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1734,6 +1958,9 @@
       <c r="E74" s="3" t="n">
         <v>0.5028450225452127</v>
       </c>
+      <c r="F74" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1751,6 +1978,9 @@
       <c r="E75" s="3" t="n">
         <v>0.5231001797857862</v>
       </c>
+      <c r="F75" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1768,6 +1998,9 @@
       <c r="E76" s="3" t="n">
         <v>0.5196184920625365</v>
       </c>
+      <c r="F76" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1785,6 +2018,9 @@
       <c r="E77" s="3" t="n">
         <v>0.5180673992399205</v>
       </c>
+      <c r="F77" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1802,6 +2038,9 @@
       <c r="E78" s="3" t="n">
         <v>0.5534931885911697</v>
       </c>
+      <c r="F78" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1818,6 +2057,9 @@
       </c>
       <c r="E79" s="3" t="n">
         <v>0.557455049278943</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1831,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1942,7 +2184,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_validated</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -2051,96 +2293,100 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S513-GROSS-A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994 Table 5.8/5.11 (r*=S*/K*, gross K*) | variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t># S513 — Marxian Profit Rate (r* = S*/(K*+V*), stock form)</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t># S513 — Marxian Profit Rate (r* = S*/(K*+V*), stock form)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>**Status**: book_period_validated</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>&lt;!-- status detail: stock-form primary; extension validated through 2024 (REVIEW_2026-07 P31 sync) --&gt;</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>&lt;!-- status detail: stock-form primary; extension validated through 2024 (REVIEW_2026-07 P31 sync) --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 central. **Units**: rate.</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 central. **Units**: rate.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>The book's central rate of profit (Shaikh &amp; Tonak 1994, §5.5 p.122): surplus value over the sum of productive capital STOCK and variable capital, in stock form. Per §5.5 footnote 16, the ideal denominator adds the stock equivalents of C* and V* to fixed capital K; the operational form used here uses K* (fixed-capital stock from BEA Fixed Assets Table 4.1 Line 1) plus V* in lieu of the unavailable circulating-capital-stock series. The flow-form variant r* = S*/(C*+V*) is retained as a secondary reference subseries S513-FLOW but is **not** the primary headline.</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>The book's central rate of profit (Shaikh &amp; Tonak 1994, §5.5 p.122): surplus value over the sum of productive capital STOCK and variable capital, in stock form. Per §5.5 footnote 16, the ideal denominator adds the stock equivalents of C* and V* to fixed capital K; the operational form used here uses K* (fixed-capital stock from BEA Fixed Assets Table 4.1 Line 1) plus V* in lieu of the unavailable circulating-capital-stock series. The flow-form variant r* = S*/(C*+V*) is retained as a secondary reference subseries S513-FLOW but is **not** the primary headline.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>&gt; **Citation + denominator note (D1, 2026-07-02).** Earlier drafts cited "Book Table 5.11" for</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>&gt; r*. The KB v2 read corrects this: **Table 5.11 is government absorption of surplus value**; the</t>
+          <t>&gt; **Citation + denominator note (D1, 2026-07-02).** Earlier drafts cited "Book Table 5.11" for</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2394,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>&gt; profit-rate table is **Table 5.8**, which defines the book's headline rate as **r* = S\*/K\***</t>
+          <t>&gt; r*. The KB v2 read corrects this: **Table 5.11 is government absorption of surplus value**; the</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2402,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>&gt; (fixed capital ONLY — *no* V* in the denominator; and K* is the book's GROSS 1987-vintage stock).</t>
+          <t>&gt; profit-rate table is **Table 5.8**, which defines the book's headline rate as **r* = S\*/K\***</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2410,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>&gt; The build's r* = S*/(K_net + V*) is thus a **denominator divergence** from the book (documented</t>
+          <t>&gt; (fixed capital ONLY — *no* V* in the denominator; and K* is the book's GROSS 1987-vintage stock).</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2418,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>&gt; under `DIV-D02`), not merely a K* vintage gap. The two forms nearly coincide early on only by</t>
+          <t>&gt; The build's r* = S*/(K_net + V*) is thus a **denominator divergence** from the book (documented</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2426,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>&gt; numeric coincidence (K_net + V* ≈ K_gross around 1948) and diverge in later years. Whether S513</t>
+          <t>&gt; under `DIV-D02`), not merely a K* vintage gap. The two forms nearly coincide early on only by</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2434,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>&gt; should adopt the book's r* = S*/K* is a separate decision beyond D1's two resolved gates and is</t>
+          <t>&gt; numeric coincidence (K_net + V* ≈ K_gross around 1948) and diverge in later years. Whether S513</t>
         </is>
       </c>
     </row>
@@ -2196,51 +2442,51 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>&gt; flagged there for a future gate. **S513 values are UNCHANGED by D1.**</t>
+          <t>&gt; should adopt the book's r* = S*/K* is a separate decision beyond D1's two resolved gates and is</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>&gt; flagged there for a future gate. **S513 values are UNCHANGED by D1.**</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>**Primary (stock form)**: r* = S505 / (S517 + S504), computed fresh per year across the full 1948-2024 span.</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>**Primary (stock form)**: r* = S505 / (S517 + S504), computed fresh per year across the full 1948-2024 span.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>- `S513-A` (1948-1989): S505-A / (S517-A + S504-A), stock form.</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>- `S513-EXT` (1998-2024): S505-COMBINED / (S517-COMBINED + S504-COMBINED), stock form. 1990-1997 absent due to upstream S504 SIC→NAICS bridge gap; no fabrication.</t>
+          <t>- `S513-A` (1948-1989): S505-A / (S517-A + S504-A), stock form.</t>
         </is>
       </c>
     </row>
@@ -2248,51 +2494,51 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>- `S513-COMBINED` (1948-2024): level concatenation of S513-A + S513-EXT. Same formula on both arms; no form-change splice.</t>
+          <t>- `S513-EXT` (1998-2024): S505-COMBINED / (S517-COMBINED + S504-COMBINED), stock form. 1990-1997 absent due to upstream S504 SIC→NAICS bridge gap; no fabrication.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>- `S513-COMBINED` (1948-2024): level concatenation of S513-A + S513-EXT. Same formula on both arms; no form-change splice.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>**Secondary (flow form, reference variant)**: `S513-FLOW` = S505-COMBINED / (S502-COMBINED + S504-COMBINED), 1948-2024. Marked `_secondary: true` in registry; provided for continuity with pre-v1.2 published flow-form headline values.</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>**Secondary (flow form, reference variant)**: `S513-FLOW` = S505-COMBINED / (S502-COMBINED + S504-COMBINED), 1948-2024. Marked `_secondary: true` in registry; provided for continuity with pre-v1.2 published flow-form headline values.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>## Sources</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>- Book Table 5.11 (Marxian rate of profit r*, 1948-1989, stock form per §5.5).</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets, current-cost net stock) → S517 K* extension.</t>
+          <t>- Book Table 5.11 (Marxian rate of profit r*, 1948-1989, stock form per §5.5).</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2546,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- BEA NIPA + BLS CES → S505 (surplus) and S504 (variable capital) extension components.</t>
+          <t>- BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets, current-cost net stock) → S517 K* extension.</t>
         </is>
       </c>
     </row>
@@ -2308,39 +2554,39 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- See S517_EPR.md, S505_EPR.md, S504_EPR.md, S502_EPR.md for component provenance.</t>
+          <t>- BEA NIPA + BLS CES → S505 (surplus) and S504 (variable capital) extension components.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- See S517_EPR.md, S505_EPR.md, S504_EPR.md, S502_EPR.md for component provenance.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>## Findings (stock-form primary, v1.2 Iter 3 regeneration)</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>## Findings (stock-form primary, v1.2 Iter 3 regeneration)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>| Year | r* (stock) | Note |</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>|------|-----------:|------|</t>
+          <t>| Year | r* (stock) | Note |</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2594,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>| 1948 | 0.3946 | Book start of period |</t>
+          <t>|------|-----------:|------|</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2602,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>| 1967 | 0.4179 | Mid-period peak |</t>
+          <t>| 1948 | 0.3946 | Book start of period |</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2610,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>| 1989 | 0.3723 | Book end of period |</t>
+          <t>| 1967 | 0.4179 | Mid-period peak |</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2618,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>| 1998 | 0.1693 | Extension start (post SIC→NAICS gap) |</t>
+          <t>| 1989 | 0.3723 | Book end of period |</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2626,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>| 2010 | 0.1620 | |</t>
+          <t>| 1998 | 0.1693 | Extension start (post SIC→NAICS gap) |</t>
         </is>
       </c>
     </row>
@@ -2388,99 +2634,99 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>| 2024 | 0.1604 | Extension end |</t>
+          <t>| 2010 | 0.1620 | |</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>| 2024 | 0.1604 | Extension end |</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>**Secular DECLINE confirmed across full 1948-2024 span** (−59.4% endpoint-to-endpoint, OLS log-trend −1.66 %/yr). This restores the book-faithful TRPF narrative of §5.5 / Ch.9 that the prior published splice had silently reversed (the legacy splice mixed book stock-form 1948-1989 with EXT flow-form 1998-2024, producing a spurious +24% rise).</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>**Secular DECLINE confirmed across full 1948-2024 span** (−59.4% endpoint-to-endpoint, OLS log-trend −1.66 %/yr). This restores the book-faithful TRPF narrative of §5.5 / Ch.9 that the prior published splice had silently reversed (the legacy splice mixed book stock-form 1948-1989 with EXT flow-form 1998-2024, producing a spurious +24% rise).</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>The 1989→1998 step (0.3723 → 0.1693, −54% in 9 years) is a real post-1989 structural break now made visible by single-formula treatment, no longer optically smoothed by silent denominator switching.</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>The 1989→1998 step (0.3723 → 0.1693, −54% in 9 years) is a real post-1989 structural break now made visible by single-formula treatment, no longer optically smoothed by silent denominator switching.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>For comparison, the secondary S513-FLOW (flow form) gives 1948=0.5227, 1989=0.6563, 2024=0.4903 — useful for variant analysis but contradicts the book's stated definition of r*.</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>For comparison, the secondary S513-FLOW (flow form) gives 1948=0.5227, 1989=0.6563, 2024=0.4903 — useful for variant analysis but contradicts the book's stated definition of r*.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>## Validator</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>## Validator</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>V03_S513 validates the S513-COMBINED stock-form series across the full 1948-2024 span: range [0.05, 1.0], secular-decline test (1948 &gt; 1989, 1948 &gt; 2024), and registry benchmarks at 1948 / 1989 / 2024.</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>V03_S513 validates the S513-COMBINED stock-form series across the full 1948-2024 span: range [0.05, 1.0], secular-decline test (1948 &gt; 1989, 1948 &gt; 2024), and registry benchmarks at 1948 / 1989 / 2024.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>## Provenance Trail</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>## Provenance Trail</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>| Version | Date | Action |</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>|---------|------|--------|</t>
+          <t>| Version | Date | Action |</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2734,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>| v1.0 | 2026-05-19 | Initial publication; book period stock-form, extension flow-form (silent form-change splice) |</t>
+          <t>|---------|------|--------|</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2742,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>| v1.1 | 2026-05-24 | Hyper-review honesty pass; status retained as book_period_validated |</t>
+          <t>| v1.0 | 2026-05-19 | Initial publication; book period stock-form, extension flow-form (silent form-change splice) |</t>
         </is>
       </c>
     </row>
@@ -2504,63 +2750,63 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>| **v1.2 Iter 3** | **2026-05-24** | **Stock-form adopted as primary across full 1948-2024 span per `docs/variants/VPR_S513_stock_vs_flow_DECISION_BRIEF.md` (HIGH confidence). P02_S513 rewritten; V03 updated; flow-form retained as S513-FLOW secondary subseries.** |</t>
+          <t>| v1.1 | 2026-05-24 | Hyper-review honesty pass; status retained as book_period_validated |</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>| **v1.2 Iter 3** | **2026-05-24** | **Stock-form adopted as primary across full 1948-2024 span per `docs/variants/VPR_S513_stock_vs_flow_DECISION_BRIEF.md` (HIGH confidence). P02_S513 rewritten; V03 updated; flow-form retained as S513-FLOW secondary subseries.** |</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion. v1.2 Iter 3 stock-form regeneration 2026-05-24.*</t>
-        </is>
-      </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion. v1.2 Iter 3 stock-form regeneration 2026-05-24.*</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
-        </is>
-      </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>**Extension refreshed by the de-splice cascade (DIV-A16).** S513-EXT now covers 1990-2024 with</t>
+          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2814,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>real components (1990-97 was NaN); 2024 = 0.1770 (was 0.1604 on the spliced V*). The registry</t>
+          <t>**Extension refreshed by the de-splice cascade (DIV-A16).** S513-EXT now covers 1990-2024 with</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2822,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024 refval 0.1604 was TAUTOLOGICAL + STALE and is queued for retirement (sole V03 FAIL at HEAD</t>
+          <t>real components (1990-97 was NaN); 2024 = 0.1770 (was 0.1604 on the spliced V*). The registry</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2830,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>until the patch is applied). Disclosed: the 1989-&gt;1990 level break (0.372-&gt;0.210) is the S517</t>
+          <t>2024 refval 0.1604 was TAUTOLOGICAL + STALE and is queued for retirement (sole V03 FAIL at HEAD</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2838,59 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
+          <t>until the patch is applied). Disclosed: the 1989-&gt;1990 level break (0.372-&gt;0.210) is the S517</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>net-K basis break (DIV-A15), not an economic event; book headline is S*/K* gross (cross-form).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>&gt; Status upgraded book_period_validated -&gt; validated_book_and_extension on 2026-07-07 (Phase-0 truth baseline, T3): populated extension block + -EXT/-COMBINED subseries + book-arm V03 PASS; parity with the pre-existing validated_book_and_extension series. See registry field `status_adjudication_2026_07_07`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>## Book-period Gross-K* variant (added 2026-07-07, K-plan WP-K4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>**Subseries `S513-GROSS-A`** (book period 1948-1989 only, `nan` beyond). Book-faithful r* = S*/K*_gross (book form, NO V*) = the book's OWN published r* (reproduces Table 5.8 to MAE 0.0025; 42/42 years exact at printed 2dp). Exposes that the shipped net+V* r* nearly coincides with the book only by a lucky cancellation, not a correct capital axis. See `VPR_S513_gross_book` in the registry, `DIVERGENCE_REGISTER.json` **DIV-070** (+ narrowed **DIV-058**), and `Handoffs/REVIEW_2026-07-07/F2_KSTAR_FIDELITY.md`. Additive only — the primary net series is unchanged; current-$ gross is non-constructible 1990-&gt; (BEA discontinued current-cost gross at the 1997 revision), so there is no extension.</t>
         </is>
       </c>
     </row>
@@ -3062,14 +3360,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3189,163 +3487,176 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>derive</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S505-A, S517-GROSS-A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>S513-GROSS-A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>r*_gross = S* / K*_gross (book form, NO V*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>output_subseries</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S513-EXT</t>
+          <t>level</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>combined_subseries</t>
+          <t>output_subseries</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S513-COMBINED</t>
+          <t>S513-EXT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, \u00a75.5 p.122 + footnote 16 (Marxian general rate of profit r* defined as ratio of surplus value to total fixed capital K; footnote 16 notes that the ideal denominator adds the stock equivalents of C* and V*); Table 5.11 (r*, 1948-1989, stock form); Figures 5.10, 5.11 (long-run profit rate, decade comparisons)", "shaikh_appendix_ref": "Table 5.11 (r*, 1948-1989, stock form per \u00a75.5 p.122); Figures 5.10, 5.11, 9.3, 9.4; identity from \u00a75.5 + Appendix H.1 with K* = fixed-capital stock + circulating-capital stock equivalents", "extension_source": "Stock-form derived: r* = S505-COMBINED / (S517-COMBINED + S504-COMBINED). Components require BEA NIPA (S505 surplus), BEA Fixed Assets Table 4.1 Line 1 (S517 capital stock K*), BEA NIPA + BLS CES (S504 variable capital V*). Same formula applied to both book period and extension; no form-change splice.", "extension_url": "https://apps.bea.gov/iTable/iTable.cfm?reqid=10&amp;step=1 (Fixed Assets Table 4.1); https://apps.bea.gov/iTable/iTable.cfm?reqid=19&amp;step=2 (NIPA); https://www.bls.gov/ces/ (CES)", "conceptual_continuity": "Marxian profit rate r* is defined in stock form per \u00a75.5 p.122 of Shaikh &amp; Tonak (1994). The book canonical denominator is fixed-capital stock K (with footnote 16 noting the ideal adds circulating-capital stock equivalents). The same stock-form formula applies across the full 1948-2024 span, computed fresh per year from extended components; no growth-rate splice. The published 1948-1989 book values in chopped/S513.csv are byte-identical to the stock-form computation, confirming the book period was always stock-form (only the prior EXT block was flow-form, which is deprecated as primary in v1.2 Iter 3).", "vintage_note": "Inherits vintage issues from S505 (surplus value), S517 (capital stock; largest single divergence is BEA 2013 R&amp;D/IPP capitalization which raised K* levels), and S504 (variable capital; SIC-&gt;NAICS bridge gap 1990-1997 propagates to S513-EXT NaN for those years rather than fabricated values).", "note": "v1.2 Iter 3 stock-form primary adoption per VPR_S513_stock_vs_flow_DECISION_BRIEF.md (HIGH confidence). Supersedes pre-v1.2 flow-form extension which is retained as secondary subseries S513-FLOW."}</t>
+          <t>S513-COMBINED</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>["S504", "S505", "S517"]</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, \u00a75.5 p.122 + footnote 16 (Marxian general rate of profit r* defined as ratio of surplus value to total fixed capital K; footnote 16 notes that the ideal denominator adds the stock equivalents of C* and V*); Table 5.11 (r*, 1948-1989, stock form); Figures 5.10, 5.11 (long-run profit rate, decade comparisons)", "shaikh_appendix_ref": "Table 5.11 (r*, 1948-1989, stock form per \u00a75.5 p.122); Figures 5.10, 5.11, 9.3, 9.4; identity from \u00a75.5 + Appendix H.1 with K* = fixed-capital stock + circulating-capital stock equivalents", "extension_source": "Stock-form derived: r* = S505-COMBINED / (S517-COMBINED + S504-COMBINED). Components require BEA NIPA (S505 surplus), BEA Fixed Assets Table 4.1 Line 1 (S517 capital stock K*), BEA NIPA + BLS CES (S504 variable capital V*). Same formula applied to both book period and extension; no form-change splice.", "extension_url": "https://apps.bea.gov/iTable/iTable.cfm?reqid=10&amp;step=1 (Fixed Assets Table 4.1); https://apps.bea.gov/iTable/iTable.cfm?reqid=19&amp;step=2 (NIPA); https://www.bls.gov/ces/ (CES)", "conceptual_continuity": "Marxian profit rate r* is defined in stock form per \u00a75.5 p.122 of Shaikh &amp; Tonak (1994). The book canonical denominator is fixed-capital stock K (with footnote 16 noting the ideal adds circulating-capital stock equivalents). The same stock-form formula applies across the full 1948-2024 span, computed fresh per year from extended components; no growth-rate splice. The published 1948-1989 book values in chopped/S513.csv are byte-identical to the stock-form computation, confirming the book period was always stock-form (only the prior EXT block was flow-form, which is deprecated as primary in v1.2 Iter 3).", "vintage_note": "Inherits vintage issues from S505 (surplus value), S517 (capital stock; largest single divergence is BEA 2013 R&amp;D/IPP capitalization which raised K* levels), and S504 (variable capital; SIC-&gt;NAICS bridge gap 1990-1997 propagates to S513-EXT NaN for those years rather than fabricated values).", "note": "v1.2 Iter 3 stock-form primary adoption per VPR_S513_stock_vs_flow_DECISION_BRIEF.md (HIGH confidence). Supersedes pre-v1.2 flow-form extension which is retained as secondary subseries S513-FLOW."}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>["S504", "S505", "S517"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>formula</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>r* = S* / (K* + V*)</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reference_values</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{"1948": 0.3946, "1989": 0.3723}</t>
-        </is>
-      </c>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>reference_values</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>{"1948": 0.3946, "1989": 0.3723}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3357,48 +3668,84 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>rate_series</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tolerance_abs</t>
+          <t>tolerance_rel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>extension_year_range</t>
+          <t>tolerance_abs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1948, 2024]</t>
+          <t>0.005</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>formula_note</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>book headline publishes r* = S*/K* (gross); pipeline PRIMARY is S*/(K*+V*) with NET K per book fn.16 - cross-form. S513-EXT covers 1990-2024 (real data post WP-A). 1989-&gt;1990 level break (0.3723-&gt;0.2098) = S517 net-K basis break (DIV-033), not an economic event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>variant_reference_values</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>{"S513-GROSS-A": {"1948": 0.39, "1949": 0.37, "1950": 0.38, "1951": 0.39, "1952": 0.38, "1953": 0.39, "1954": 0.38, "1955": 0.39, "1956": 0.36, "1957": 0.36, "1958": 0.36, "1959": 0.38, "1960": 0.38, "1961": 0.38, "1962": 0.4, "1963": 0.41, "1964": 0.42, "1965": 0.42, "1966": 0.42, "1967": 0.42, "1968": 0.41, "1969": 0.4, "1970": 0.38, "1971": 0.37, "1972": 0.37, "1973": 0.37, "1974": 0.33, "1975": 0.33, "1976": 0.33, "1977": 0.33, "1978": 0.32, "1979": 0.32, "1980": 0.3, "1981": 0.3, "1982": 0.29, "1983": 0.31, "1984": 0.33, "1985": 0.34, "1986": 0.34, "1987": 0.34, "1988": 0.35, "1989": 0.35}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>variant_reference_values_note</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S513-GROSS-A = book Table 5.8 published r* (S*/K*_gross), full column. Build reproduces it to MAE 0.0025 (max 0.0045); 42/42 years EXACT at printed 2dp. Book-anchored INDEPENDENT reference values (printed book Table 5.8 / 5.7 / 5.11 cells, KB v2 _combined/5.8.csv; full 1948-1989 column). Checked by V03 against the S*-GROSS-A book-faithful variant. Unlike validation.reference_values (tautological = loader output, A1), these are the book's OWN published numbers -&gt; the r*/r*' family's first independent book anchor (F2 2026-07-07, K-plan WP-K3).</t>
         </is>
       </c>
     </row>
